--- a/data/condiciones.xlsx
+++ b/data/condiciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://novacero-my.sharepoint.com/personal/guilcapip_novacero_com/Documents/Escritorio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A7A89CA-9448-4C3B-9C0A-3ED9418F6A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEE92238-EF98-4D34-90B2-405F61396E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2889" uniqueCount="1008">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2908" uniqueCount="1016">
   <si>
     <t>BASE CONDICIONES Y ACCIONES  INSEGURAS 2026</t>
   </si>
@@ -3167,6 +3167,30 @@
   </si>
   <si>
     <t>Despejar la salida de emergencia</t>
+  </si>
+  <si>
+    <t>Mandos sin etiquetar en maquinaria</t>
+  </si>
+  <si>
+    <t>Etiquetar mandos</t>
+  </si>
+  <si>
+    <t>Químico sin etiquetado</t>
+  </si>
+  <si>
+    <t>Compras producción</t>
+  </si>
+  <si>
+    <t>Incumplimiento al procedimiento</t>
+  </si>
+  <si>
+    <t>Compras</t>
+  </si>
+  <si>
+    <t>Alvaro Tapia</t>
+  </si>
+  <si>
+    <t>Etiquetar con sistema HMIS</t>
   </si>
 </sst>
 </file>
@@ -3336,7 +3360,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3351,12 +3375,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3371,13 +3390,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -3392,6 +3416,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3673,94 +3700,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M357"/>
+  <dimension ref="A1:M359"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.42578125" style="4"/>
-    <col min="5" max="5" width="35.140625" customWidth="1"/>
+    <col min="3" max="3" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="24.28515625" customWidth="1"/>
+    <col min="7" max="7" width="61.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="23.5703125" customWidth="1"/>
+    <col min="11" max="11" width="23.140625" customWidth="1"/>
     <col min="13" max="13" width="34.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="15" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="15" t="s">
         <v>10</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="L2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="18"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
       <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
       <c r="K3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1">
@@ -15890,40 +15919,40 @@
       </c>
       <c r="M347" s="11"/>
     </row>
-    <row r="348" spans="1:13" ht="30.75">
+    <row r="348" spans="1:13" ht="30">
       <c r="A348" s="8">
         <v>345</v>
       </c>
-      <c r="B348" s="12">
+      <c r="B348" s="19">
         <v>46226</v>
       </c>
-      <c r="C348" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D348" s="13" t="s">
+      <c r="C348" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D348" s="20" t="s">
         <v>981</v>
       </c>
-      <c r="E348" s="13"/>
-      <c r="F348" s="13" t="s">
+      <c r="E348" s="20"/>
+      <c r="F348" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="G348" s="13" t="s">
+      <c r="G348" s="20" t="s">
         <v>758</v>
       </c>
-      <c r="H348" s="14" t="s">
+      <c r="H348" s="21" t="s">
         <v>982</v>
       </c>
-      <c r="I348" s="14" t="s">
+      <c r="I348" s="21" t="s">
         <v>983</v>
       </c>
-      <c r="J348" s="15" t="s">
+      <c r="J348" s="22" t="s">
         <v>984</v>
       </c>
-      <c r="K348" s="15"/>
-      <c r="L348" s="13" t="s">
+      <c r="K348" s="22"/>
+      <c r="L348" s="20" t="s">
         <v>509</v>
       </c>
-      <c r="M348" s="13"/>
+      <c r="M348" s="20"/>
     </row>
     <row r="349" spans="1:13" ht="75" customHeight="1">
       <c r="A349" s="9">
@@ -15935,10 +15964,10 @@
       <c r="C349" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D349" s="16" t="s">
+      <c r="D349" s="13" t="s">
         <v>985</v>
       </c>
-      <c r="E349" s="16"/>
+      <c r="E349" s="13"/>
       <c r="F349" s="7" t="s">
         <v>986</v>
       </c>
@@ -15951,119 +15980,119 @@
       <c r="I349" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="J349" s="16" t="s">
+      <c r="J349" s="13" t="s">
         <v>988</v>
       </c>
-      <c r="K349" s="20"/>
+      <c r="K349" s="12"/>
       <c r="L349" s="6" t="s">
         <v>509</v>
       </c>
       <c r="M349" s="6"/>
     </row>
     <row r="350" spans="1:13" ht="60.75" customHeight="1">
-      <c r="A350" s="13">
+      <c r="A350" s="20">
         <v>347</v>
       </c>
       <c r="B350" s="23">
         <v>46226</v>
       </c>
-      <c r="C350" s="13" t="s">
+      <c r="C350" s="20" t="s">
         <v>50</v>
       </c>
       <c r="D350" s="24" t="s">
         <v>989</v>
       </c>
       <c r="E350" s="25"/>
-      <c r="F350" s="13" t="s">
+      <c r="F350" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="G350" s="13" t="s">
+      <c r="G350" s="20" t="s">
         <v>688</v>
       </c>
-      <c r="H350" s="14" t="s">
+      <c r="H350" s="21" t="s">
         <v>990</v>
       </c>
-      <c r="I350" s="13" t="s">
+      <c r="I350" s="20" t="s">
         <v>901</v>
       </c>
       <c r="J350" s="24" t="s">
         <v>991</v>
       </c>
       <c r="K350" s="26"/>
-      <c r="L350" s="13" t="s">
+      <c r="L350" s="20" t="s">
         <v>509</v>
       </c>
-      <c r="M350" s="13"/>
+      <c r="M350" s="20"/>
     </row>
     <row r="351" spans="1:13" ht="45.75" customHeight="1">
-      <c r="A351" s="13">
+      <c r="A351" s="20">
         <v>348</v>
       </c>
-      <c r="B351" s="12">
+      <c r="B351" s="19">
         <v>46226</v>
       </c>
-      <c r="C351" s="13" t="s">
+      <c r="C351" s="20" t="s">
         <v>16</v>
       </c>
       <c r="D351" s="24" t="s">
         <v>992</v>
       </c>
       <c r="E351" s="25"/>
-      <c r="F351" s="13" t="s">
+      <c r="F351" s="20" t="s">
         <v>993</v>
       </c>
-      <c r="G351" s="13" t="s">
+      <c r="G351" s="20" t="s">
         <v>994</v>
       </c>
-      <c r="H351" s="13" t="s">
+      <c r="H351" s="20" t="s">
         <v>993</v>
       </c>
-      <c r="I351" s="13" t="s">
+      <c r="I351" s="20" t="s">
         <v>32</v>
       </c>
       <c r="J351" s="27" t="s">
         <v>995</v>
       </c>
       <c r="K351" s="26"/>
-      <c r="L351" s="13" t="s">
+      <c r="L351" s="20" t="s">
         <v>509</v>
       </c>
-      <c r="M351" s="13"/>
-    </row>
-    <row r="352" spans="1:13" ht="30.75">
-      <c r="A352" s="13">
+      <c r="M351" s="20"/>
+    </row>
+    <row r="352" spans="1:13" ht="46.5" customHeight="1">
+      <c r="A352" s="20">
         <v>349</v>
       </c>
-      <c r="B352" s="12">
+      <c r="B352" s="19">
         <v>46219</v>
       </c>
-      <c r="C352" s="13" t="s">
+      <c r="C352" s="20" t="s">
         <v>50</v>
       </c>
       <c r="D352" s="24" t="s">
         <v>996</v>
       </c>
       <c r="E352" s="26"/>
-      <c r="F352" s="13" t="s">
+      <c r="F352" s="20" t="s">
         <v>993</v>
       </c>
-      <c r="G352" s="14" t="s">
+      <c r="G352" s="21" t="s">
         <v>997</v>
       </c>
-      <c r="H352" s="13" t="s">
+      <c r="H352" s="20" t="s">
         <v>993</v>
       </c>
-      <c r="I352" s="13" t="s">
+      <c r="I352" s="20" t="s">
         <v>32</v>
       </c>
       <c r="J352" s="27" t="s">
         <v>995</v>
       </c>
       <c r="K352" s="26"/>
-      <c r="L352" s="13" t="s">
+      <c r="L352" s="20" t="s">
         <v>509</v>
       </c>
-      <c r="M352" s="13"/>
+      <c r="M352" s="20"/>
     </row>
     <row r="353" spans="1:13" ht="76.5" customHeight="1">
       <c r="A353" s="6">
@@ -16075,10 +16104,10 @@
       <c r="C353" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D353" s="16" t="s">
+      <c r="D353" s="13" t="s">
         <v>998</v>
       </c>
-      <c r="E353" s="16"/>
+      <c r="E353" s="13"/>
       <c r="F353" s="6" t="s">
         <v>153</v>
       </c>
@@ -16091,10 +16120,10 @@
       <c r="I353" s="6" t="s">
         <v>917</v>
       </c>
-      <c r="J353" s="21" t="s">
+      <c r="J353" s="17" t="s">
         <v>999</v>
       </c>
-      <c r="K353" s="22"/>
+      <c r="K353" s="18"/>
       <c r="L353" s="6" t="s">
         <v>509</v>
       </c>
@@ -16110,10 +16139,10 @@
       <c r="C354" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D354" s="16" t="s">
+      <c r="D354" s="13" t="s">
         <v>1000</v>
       </c>
-      <c r="E354" s="16"/>
+      <c r="E354" s="13"/>
       <c r="F354" s="6" t="s">
         <v>153</v>
       </c>
@@ -16126,10 +16155,10 @@
       <c r="I354" s="6" t="s">
         <v>917</v>
       </c>
-      <c r="J354" s="21" t="s">
+      <c r="J354" s="17" t="s">
         <v>1001</v>
       </c>
-      <c r="K354" s="22"/>
+      <c r="K354" s="18"/>
       <c r="L354" s="6" t="s">
         <v>509</v>
       </c>
@@ -16142,13 +16171,13 @@
       <c r="B355" s="5">
         <v>46218</v>
       </c>
-      <c r="C355" s="5">
-        <v>46219</v>
-      </c>
-      <c r="D355" s="16" t="s">
+      <c r="C355" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D355" s="13" t="s">
         <v>1002</v>
       </c>
-      <c r="E355" s="16"/>
+      <c r="E355" s="13"/>
       <c r="F355" s="6" t="s">
         <v>122</v>
       </c>
@@ -16161,10 +16190,10 @@
       <c r="I355" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="J355" s="21" t="s">
+      <c r="J355" s="17" t="s">
         <v>999</v>
       </c>
-      <c r="K355" s="22"/>
+      <c r="K355" s="18"/>
       <c r="L355" s="6" t="s">
         <v>509</v>
       </c>
@@ -16177,13 +16206,13 @@
       <c r="B356" s="5">
         <v>46218</v>
       </c>
-      <c r="C356" s="5">
-        <v>46223</v>
-      </c>
-      <c r="D356" s="16" t="s">
+      <c r="C356" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D356" s="13" t="s">
         <v>1004</v>
       </c>
-      <c r="E356" s="16"/>
+      <c r="E356" s="13"/>
       <c r="F356" s="6" t="s">
         <v>122</v>
       </c>
@@ -16196,67 +16225,147 @@
       <c r="I356" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="J356" s="21" t="s">
+      <c r="J356" s="17" t="s">
         <v>1005</v>
       </c>
-      <c r="K356" s="22"/>
+      <c r="K356" s="18"/>
       <c r="L356" s="6" t="s">
         <v>509</v>
       </c>
       <c r="M356" s="6"/>
     </row>
     <row r="357" spans="1:13">
-      <c r="A357" s="6">
+      <c r="A357" s="20">
         <v>354</v>
       </c>
-      <c r="B357" s="5">
+      <c r="B357" s="19">
         <v>46218</v>
       </c>
-      <c r="C357" s="5">
-        <v>46223</v>
-      </c>
-      <c r="D357" s="16" t="s">
+      <c r="C357" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D357" s="28" t="s">
         <v>1006</v>
       </c>
-      <c r="E357" s="16"/>
-      <c r="F357" s="6" t="s">
+      <c r="E357" s="28"/>
+      <c r="F357" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="G357" s="6" t="s">
+      <c r="G357" s="20" t="s">
         <v>959</v>
       </c>
-      <c r="H357" s="6" t="s">
+      <c r="H357" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="I357" s="6" t="s">
+      <c r="I357" s="20" t="s">
         <v>507</v>
       </c>
-      <c r="J357" s="21" t="s">
+      <c r="J357" s="27" t="s">
         <v>1007</v>
       </c>
-      <c r="K357" s="22"/>
-      <c r="L357" s="6" t="s">
+      <c r="K357" s="26"/>
+      <c r="L357" s="20" t="s">
         <v>509</v>
       </c>
-      <c r="M357" s="6"/>
+      <c r="M357" s="20"/>
+    </row>
+    <row r="358" spans="1:13" ht="30.75">
+      <c r="A358" s="6">
+        <v>355</v>
+      </c>
+      <c r="B358" s="5">
+        <v>46218</v>
+      </c>
+      <c r="C358" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D358" s="13" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E358" s="13"/>
+      <c r="F358" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="G358" s="6" t="s">
+        <v>831</v>
+      </c>
+      <c r="H358" s="7" t="s">
+        <v>990</v>
+      </c>
+      <c r="I358" s="6" t="s">
+        <v>917</v>
+      </c>
+      <c r="J358" s="12" t="s">
+        <v>1009</v>
+      </c>
+      <c r="K358" s="12"/>
+      <c r="L358" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="M358" s="6"/>
+    </row>
+    <row r="359" spans="1:13">
+      <c r="A359" s="6">
+        <v>356</v>
+      </c>
+      <c r="B359" s="5">
+        <v>46226</v>
+      </c>
+      <c r="C359" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D359" s="17" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E359" s="18"/>
+      <c r="F359" s="6" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G359" s="6" t="s">
+        <v>1012</v>
+      </c>
+      <c r="H359" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="I359" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="J359" s="17" t="s">
+        <v>1015</v>
+      </c>
+      <c r="K359" s="18"/>
+      <c r="L359" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="M359" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N353" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="31">
+  <autoFilter ref="A2:N2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <mergeCells count="35">
+    <mergeCell ref="D359:E359"/>
+    <mergeCell ref="J359:K359"/>
+    <mergeCell ref="D356:E356"/>
+    <mergeCell ref="J356:K356"/>
     <mergeCell ref="D357:E357"/>
     <mergeCell ref="J357:K357"/>
+    <mergeCell ref="D358:E358"/>
+    <mergeCell ref="J358:K358"/>
+    <mergeCell ref="D353:E353"/>
+    <mergeCell ref="J353:K353"/>
     <mergeCell ref="D354:E354"/>
     <mergeCell ref="J354:K354"/>
     <mergeCell ref="D355:E355"/>
     <mergeCell ref="J355:K355"/>
-    <mergeCell ref="D356:E356"/>
-    <mergeCell ref="J356:K356"/>
+    <mergeCell ref="D350:E350"/>
+    <mergeCell ref="J350:K350"/>
     <mergeCell ref="D351:E351"/>
     <mergeCell ref="J351:K351"/>
     <mergeCell ref="D352:E352"/>
     <mergeCell ref="J352:K352"/>
-    <mergeCell ref="D353:E353"/>
-    <mergeCell ref="J353:K353"/>
+    <mergeCell ref="J348:K348"/>
+    <mergeCell ref="D349:E349"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A2:A3"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="M2:M3"/>
     <mergeCell ref="L2:L3"/>
@@ -16267,13 +16376,7 @@
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D350:E350"/>
-    <mergeCell ref="J348:K348"/>
-    <mergeCell ref="D349:E349"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
     <mergeCell ref="J349:K349"/>
-    <mergeCell ref="J350:K350"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -16281,6 +16384,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ffec3ae9-8fcb-4d01-9912-d9c8acfa0edd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="f744fce7-bf87-44de-8eb1-9fa1455f46be" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ffec3ae9-8fcb-4d01-9912-d9c8acfa0edd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010086942A3F34A68F4FA889A03CFBAE991E" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a9c9023ec2ee2a8c54e6ffbc5348479d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ffec3ae9-8fcb-4d01-9912-d9c8acfa0edd" xmlns:ns3="f744fce7-bf87-44de-8eb1-9fa1455f46be" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="976732c5a9512de0261515c98037693f" ns2:_="" ns3:_="">
     <xsd:import namespace="ffec3ae9-8fcb-4d01-9912-d9c8acfa0edd"/>
@@ -16499,35 +16623,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ffec3ae9-8fcb-4d01-9912-d9c8acfa0edd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f744fce7-bf87-44de-8eb1-9fa1455f46be" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ffec3ae9-8fcb-4d01-9912-d9c8acfa0edd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B182A765-8CFD-450C-AF9F-37AEC630B2B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7F4C917-C929-4E8D-89EB-6D6A5A32B05F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7F4C917-C929-4E8D-89EB-6D6A5A32B05F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{198F9FE4-CC7D-449E-8B79-8976DE4CC7F7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{198F9FE4-CC7D-449E-8B79-8976DE4CC7F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B182A765-8CFD-450C-AF9F-37AEC630B2B6}"/>
 </file>
--- a/data/condiciones.xlsx
+++ b/data/condiciones.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30317"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://novacero-my.sharepoint.com/personal/guilcapip_novacero_com/Documents/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mayancelad\OneDrive - NOVACERO S.A\Escritorio\PROD\CELULAS\NOVA SAFE\SAFEFLOW\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FEE92238-EF98-4D34-90B2-405F61396E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,23 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$2:$N$2</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -3196,8 +3179,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3222,7 +3205,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -3296,19 +3279,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -3347,20 +3317,46 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3375,51 +3371,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3699,99 +3682,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M359"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M361"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.42578125" style="4"/>
-    <col min="3" max="3" width="34.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.44140625" customWidth="1"/>
     <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="61.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="61.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="23.5703125" customWidth="1"/>
-    <col min="11" max="11" width="23.140625" customWidth="1"/>
-    <col min="13" max="13" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.5546875" customWidth="1"/>
+    <col min="10" max="10" width="126.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.109375" customWidth="1"/>
+    <col min="13" max="13" width="34.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="15" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="27"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="22" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="22" t="s">
         <v>10</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="22" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="15"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="23"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
       <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
       <c r="K3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3828,7 +3812,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -3865,7 +3849,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -3902,7 +3886,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>4</v>
       </c>
@@ -3939,7 +3923,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>5</v>
       </c>
@@ -3976,7 +3960,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>6</v>
       </c>
@@ -4013,7 +3997,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>7</v>
       </c>
@@ -4050,7 +4034,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>8</v>
       </c>
@@ -4087,7 +4071,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>9</v>
       </c>
@@ -4124,7 +4108,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>10</v>
       </c>
@@ -4161,7 +4145,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>11</v>
       </c>
@@ -4198,7 +4182,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>12</v>
       </c>
@@ -4235,7 +4219,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>13</v>
       </c>
@@ -4272,7 +4256,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>14</v>
       </c>
@@ -4307,7 +4291,7 @@
       </c>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>15</v>
       </c>
@@ -4344,7 +4328,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>16</v>
       </c>
@@ -4381,7 +4365,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -4418,7 +4402,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>18</v>
       </c>
@@ -4455,7 +4439,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>19</v>
       </c>
@@ -4492,7 +4476,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -4529,7 +4513,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -4566,7 +4550,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -4603,7 +4587,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>23</v>
       </c>
@@ -4640,7 +4624,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>24</v>
       </c>
@@ -4677,7 +4661,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>25</v>
       </c>
@@ -4714,7 +4698,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>26</v>
       </c>
@@ -4751,7 +4735,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>27</v>
       </c>
@@ -4788,7 +4772,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -4825,7 +4809,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>29</v>
       </c>
@@ -4862,7 +4846,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -4899,7 +4883,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>31</v>
       </c>
@@ -4936,7 +4920,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>32</v>
       </c>
@@ -4973,7 +4957,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>33</v>
       </c>
@@ -5010,7 +4994,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>34</v>
       </c>
@@ -5047,7 +5031,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>35</v>
       </c>
@@ -5084,7 +5068,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>36</v>
       </c>
@@ -5121,7 +5105,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>37</v>
       </c>
@@ -5158,7 +5142,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>38</v>
       </c>
@@ -5195,7 +5179,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>39</v>
       </c>
@@ -5232,7 +5216,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>40</v>
       </c>
@@ -5269,7 +5253,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>41</v>
       </c>
@@ -5304,7 +5288,7 @@
       </c>
       <c r="M44" s="1"/>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>42</v>
       </c>
@@ -5339,7 +5323,7 @@
       </c>
       <c r="M45" s="1"/>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>43</v>
       </c>
@@ -5374,7 +5358,7 @@
       </c>
       <c r="M46" s="1"/>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>44</v>
       </c>
@@ -5409,7 +5393,7 @@
       </c>
       <c r="M47" s="1"/>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>45</v>
       </c>
@@ -5444,7 +5428,7 @@
       </c>
       <c r="M48" s="1"/>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46</v>
       </c>
@@ -5479,7 +5463,7 @@
       </c>
       <c r="M49" s="1"/>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>47</v>
       </c>
@@ -5514,7 +5498,7 @@
       </c>
       <c r="M50" s="1"/>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>48</v>
       </c>
@@ -5549,7 +5533,7 @@
       </c>
       <c r="M51" s="1"/>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>49</v>
       </c>
@@ -5584,7 +5568,7 @@
       </c>
       <c r="M52" s="1"/>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>50</v>
       </c>
@@ -5619,7 +5603,7 @@
       </c>
       <c r="M53" s="1"/>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>51</v>
       </c>
@@ -5654,7 +5638,7 @@
       </c>
       <c r="M54" s="1"/>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>52</v>
       </c>
@@ -5689,7 +5673,7 @@
       </c>
       <c r="M55" s="1"/>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>53</v>
       </c>
@@ -5724,7 +5708,7 @@
       </c>
       <c r="M56" s="1"/>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>54</v>
       </c>
@@ -5759,7 +5743,7 @@
       </c>
       <c r="M57" s="1"/>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>55</v>
       </c>
@@ -5794,7 +5778,7 @@
       </c>
       <c r="M58" s="1"/>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>56</v>
       </c>
@@ -5829,7 +5813,7 @@
       </c>
       <c r="M59" s="1"/>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>57</v>
       </c>
@@ -5864,7 +5848,7 @@
       </c>
       <c r="M60" s="1"/>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>58</v>
       </c>
@@ -5899,7 +5883,7 @@
       </c>
       <c r="M61" s="1"/>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>59</v>
       </c>
@@ -5934,7 +5918,7 @@
       </c>
       <c r="M62" s="1"/>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>60</v>
       </c>
@@ -5969,7 +5953,7 @@
       </c>
       <c r="M63" s="1"/>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>61</v>
       </c>
@@ -6004,7 +5988,7 @@
       </c>
       <c r="M64" s="1"/>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>62</v>
       </c>
@@ -6039,7 +6023,7 @@
       </c>
       <c r="M65" s="1"/>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>63</v>
       </c>
@@ -6074,7 +6058,7 @@
       </c>
       <c r="M66" s="1"/>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>64</v>
       </c>
@@ -6109,7 +6093,7 @@
       </c>
       <c r="M67" s="1"/>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>65</v>
       </c>
@@ -6144,7 +6128,7 @@
       </c>
       <c r="M68" s="1"/>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>66</v>
       </c>
@@ -6179,7 +6163,7 @@
       </c>
       <c r="M69" s="1"/>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>67</v>
       </c>
@@ -6214,7 +6198,7 @@
       </c>
       <c r="M70" s="1"/>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>68</v>
       </c>
@@ -6249,7 +6233,7 @@
       </c>
       <c r="M71" s="1"/>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>69</v>
       </c>
@@ -6284,7 +6268,7 @@
       </c>
       <c r="M72" s="1"/>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>70</v>
       </c>
@@ -6319,7 +6303,7 @@
       </c>
       <c r="M73" s="1"/>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>71</v>
       </c>
@@ -6354,7 +6338,7 @@
       </c>
       <c r="M74" s="1"/>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>72</v>
       </c>
@@ -6389,7 +6373,7 @@
       </c>
       <c r="M75" s="1"/>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>73</v>
       </c>
@@ -6424,7 +6408,7 @@
       </c>
       <c r="M76" s="1"/>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>74</v>
       </c>
@@ -6459,7 +6443,7 @@
       </c>
       <c r="M77" s="1"/>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>75</v>
       </c>
@@ -6494,7 +6478,7 @@
       </c>
       <c r="M78" s="1"/>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>76</v>
       </c>
@@ -6529,7 +6513,7 @@
       </c>
       <c r="M79" s="1"/>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>77</v>
       </c>
@@ -6564,7 +6548,7 @@
       </c>
       <c r="M80" s="1"/>
     </row>
-    <row r="81" spans="1:13">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>78</v>
       </c>
@@ -6599,7 +6583,7 @@
       </c>
       <c r="M81" s="1"/>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>79</v>
       </c>
@@ -6634,7 +6618,7 @@
       </c>
       <c r="M82" s="1"/>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>80</v>
       </c>
@@ -6669,7 +6653,7 @@
       </c>
       <c r="M83" s="1"/>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>81</v>
       </c>
@@ -6704,7 +6688,7 @@
       </c>
       <c r="M84" s="1"/>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>82</v>
       </c>
@@ -6739,7 +6723,7 @@
       </c>
       <c r="M85" s="1"/>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>83</v>
       </c>
@@ -6774,7 +6758,7 @@
       </c>
       <c r="M86" s="1"/>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>84</v>
       </c>
@@ -6809,7 +6793,7 @@
       </c>
       <c r="M87" s="1"/>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>85</v>
       </c>
@@ -6844,7 +6828,7 @@
       </c>
       <c r="M88" s="1"/>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>86</v>
       </c>
@@ -6879,7 +6863,7 @@
       </c>
       <c r="M89" s="1"/>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>87</v>
       </c>
@@ -6914,7 +6898,7 @@
       </c>
       <c r="M90" s="1"/>
     </row>
-    <row r="91" spans="1:13">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>88</v>
       </c>
@@ -6949,7 +6933,7 @@
       </c>
       <c r="M91" s="1"/>
     </row>
-    <row r="92" spans="1:13">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>89</v>
       </c>
@@ -6984,7 +6968,7 @@
       </c>
       <c r="M92" s="1"/>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>90</v>
       </c>
@@ -7019,7 +7003,7 @@
       </c>
       <c r="M93" s="1"/>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>91</v>
       </c>
@@ -7054,7 +7038,7 @@
       </c>
       <c r="M94" s="1"/>
     </row>
-    <row r="95" spans="1:13">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>92</v>
       </c>
@@ -7089,7 +7073,7 @@
       </c>
       <c r="M95" s="1"/>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>93</v>
       </c>
@@ -7124,7 +7108,7 @@
       </c>
       <c r="M96" s="1"/>
     </row>
-    <row r="97" spans="1:13">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>94</v>
       </c>
@@ -7159,7 +7143,7 @@
       </c>
       <c r="M97" s="1"/>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>95</v>
       </c>
@@ -7194,7 +7178,7 @@
       </c>
       <c r="M98" s="1"/>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>96</v>
       </c>
@@ -7229,7 +7213,7 @@
       </c>
       <c r="M99" s="1"/>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>97</v>
       </c>
@@ -7264,7 +7248,7 @@
       </c>
       <c r="M100" s="1"/>
     </row>
-    <row r="101" spans="1:13">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>98</v>
       </c>
@@ -7299,7 +7283,7 @@
       </c>
       <c r="M101" s="1"/>
     </row>
-    <row r="102" spans="1:13">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>99</v>
       </c>
@@ -7334,7 +7318,7 @@
       </c>
       <c r="M102" s="1"/>
     </row>
-    <row r="103" spans="1:13">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>100</v>
       </c>
@@ -7369,7 +7353,7 @@
       </c>
       <c r="M103" s="1"/>
     </row>
-    <row r="104" spans="1:13">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>101</v>
       </c>
@@ -7404,7 +7388,7 @@
       </c>
       <c r="M104" s="1"/>
     </row>
-    <row r="105" spans="1:13">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>102</v>
       </c>
@@ -7439,7 +7423,7 @@
       </c>
       <c r="M105" s="1"/>
     </row>
-    <row r="106" spans="1:13">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>103</v>
       </c>
@@ -7474,7 +7458,7 @@
       </c>
       <c r="M106" s="1"/>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>104</v>
       </c>
@@ -7509,7 +7493,7 @@
       </c>
       <c r="M107" s="1"/>
     </row>
-    <row r="108" spans="1:13">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>105</v>
       </c>
@@ -7544,7 +7528,7 @@
       </c>
       <c r="M108" s="1"/>
     </row>
-    <row r="109" spans="1:13">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>106</v>
       </c>
@@ -7579,7 +7563,7 @@
       </c>
       <c r="M109" s="1"/>
     </row>
-    <row r="110" spans="1:13">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>107</v>
       </c>
@@ -7614,7 +7598,7 @@
       </c>
       <c r="M110" s="1"/>
     </row>
-    <row r="111" spans="1:13">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>108</v>
       </c>
@@ -7649,7 +7633,7 @@
       </c>
       <c r="M111" s="1"/>
     </row>
-    <row r="112" spans="1:13">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>109</v>
       </c>
@@ -7684,7 +7668,7 @@
       </c>
       <c r="M112" s="1"/>
     </row>
-    <row r="113" spans="1:13">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>110</v>
       </c>
@@ -7719,7 +7703,7 @@
       </c>
       <c r="M113" s="1"/>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>111</v>
       </c>
@@ -7754,7 +7738,7 @@
       </c>
       <c r="M114" s="1"/>
     </row>
-    <row r="115" spans="1:13">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>112</v>
       </c>
@@ -7789,7 +7773,7 @@
       </c>
       <c r="M115" s="1"/>
     </row>
-    <row r="116" spans="1:13">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>113</v>
       </c>
@@ -7824,7 +7808,7 @@
       </c>
       <c r="M116" s="1"/>
     </row>
-    <row r="117" spans="1:13">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>114</v>
       </c>
@@ -7859,7 +7843,7 @@
       </c>
       <c r="M117" s="1"/>
     </row>
-    <row r="118" spans="1:13">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>115</v>
       </c>
@@ -7894,7 +7878,7 @@
       </c>
       <c r="M118" s="1"/>
     </row>
-    <row r="119" spans="1:13">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>116</v>
       </c>
@@ -7929,7 +7913,7 @@
       </c>
       <c r="M119" s="1"/>
     </row>
-    <row r="120" spans="1:13">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>117</v>
       </c>
@@ -7964,7 +7948,7 @@
       </c>
       <c r="M120" s="1"/>
     </row>
-    <row r="121" spans="1:13">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>118</v>
       </c>
@@ -7999,7 +7983,7 @@
       </c>
       <c r="M121" s="1"/>
     </row>
-    <row r="122" spans="1:13">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>119</v>
       </c>
@@ -8034,7 +8018,7 @@
       </c>
       <c r="M122" s="1"/>
     </row>
-    <row r="123" spans="1:13">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>120</v>
       </c>
@@ -8069,7 +8053,7 @@
       </c>
       <c r="M123" s="1"/>
     </row>
-    <row r="124" spans="1:13">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>121</v>
       </c>
@@ -8104,7 +8088,7 @@
       </c>
       <c r="M124" s="1"/>
     </row>
-    <row r="125" spans="1:13">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>122</v>
       </c>
@@ -8139,7 +8123,7 @@
       </c>
       <c r="M125" s="1"/>
     </row>
-    <row r="126" spans="1:13">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>123</v>
       </c>
@@ -8174,7 +8158,7 @@
       </c>
       <c r="M126" s="1"/>
     </row>
-    <row r="127" spans="1:13">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>124</v>
       </c>
@@ -8209,7 +8193,7 @@
       </c>
       <c r="M127" s="1"/>
     </row>
-    <row r="128" spans="1:13">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>125</v>
       </c>
@@ -8244,7 +8228,7 @@
       </c>
       <c r="M128" s="1"/>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>126</v>
       </c>
@@ -8279,7 +8263,7 @@
       </c>
       <c r="M129" s="1"/>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>127</v>
       </c>
@@ -8314,7 +8298,7 @@
       </c>
       <c r="M130" s="1"/>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>128</v>
       </c>
@@ -8349,7 +8333,7 @@
       </c>
       <c r="M131" s="1"/>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>129</v>
       </c>
@@ -8384,7 +8368,7 @@
       </c>
       <c r="M132" s="1"/>
     </row>
-    <row r="133" spans="1:13">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>130</v>
       </c>
@@ -8419,7 +8403,7 @@
       </c>
       <c r="M133" s="1"/>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>131</v>
       </c>
@@ -8454,7 +8438,7 @@
       </c>
       <c r="M134" s="1"/>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>132</v>
       </c>
@@ -8489,7 +8473,7 @@
       </c>
       <c r="M135" s="1"/>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>133</v>
       </c>
@@ -8524,7 +8508,7 @@
       </c>
       <c r="M136" s="1"/>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>134</v>
       </c>
@@ -8559,7 +8543,7 @@
       </c>
       <c r="M137" s="1"/>
     </row>
-    <row r="138" spans="1:13">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>135</v>
       </c>
@@ -8594,7 +8578,7 @@
       </c>
       <c r="M138" s="1"/>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>136</v>
       </c>
@@ -8629,7 +8613,7 @@
       </c>
       <c r="M139" s="1"/>
     </row>
-    <row r="140" spans="1:13">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>137</v>
       </c>
@@ -8664,7 +8648,7 @@
       </c>
       <c r="M140" s="1"/>
     </row>
-    <row r="141" spans="1:13">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>138</v>
       </c>
@@ -8699,7 +8683,7 @@
       </c>
       <c r="M141" s="1"/>
     </row>
-    <row r="142" spans="1:13">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>139</v>
       </c>
@@ -8734,7 +8718,7 @@
       </c>
       <c r="M142" s="1"/>
     </row>
-    <row r="143" spans="1:13">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>140</v>
       </c>
@@ -8769,7 +8753,7 @@
       </c>
       <c r="M143" s="1"/>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>141</v>
       </c>
@@ -8804,7 +8788,7 @@
       </c>
       <c r="M144" s="1"/>
     </row>
-    <row r="145" spans="1:13">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>142</v>
       </c>
@@ -8839,7 +8823,7 @@
       </c>
       <c r="M145" s="1"/>
     </row>
-    <row r="146" spans="1:13">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>143</v>
       </c>
@@ -8874,7 +8858,7 @@
       </c>
       <c r="M146" s="1"/>
     </row>
-    <row r="147" spans="1:13">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>144</v>
       </c>
@@ -8909,7 +8893,7 @@
       </c>
       <c r="M147" s="1"/>
     </row>
-    <row r="148" spans="1:13">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>145</v>
       </c>
@@ -8944,7 +8928,7 @@
       </c>
       <c r="M148" s="1"/>
     </row>
-    <row r="149" spans="1:13">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>146</v>
       </c>
@@ -8979,7 +8963,7 @@
       </c>
       <c r="M149" s="1"/>
     </row>
-    <row r="150" spans="1:13">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>147</v>
       </c>
@@ -9014,7 +8998,7 @@
       </c>
       <c r="M150" s="1"/>
     </row>
-    <row r="151" spans="1:13">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>148</v>
       </c>
@@ -9049,7 +9033,7 @@
       </c>
       <c r="M151" s="1"/>
     </row>
-    <row r="152" spans="1:13">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>149</v>
       </c>
@@ -9084,7 +9068,7 @@
       </c>
       <c r="M152" s="1"/>
     </row>
-    <row r="153" spans="1:13">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>150</v>
       </c>
@@ -9119,7 +9103,7 @@
       </c>
       <c r="M153" s="1"/>
     </row>
-    <row r="154" spans="1:13">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>151</v>
       </c>
@@ -9154,7 +9138,7 @@
       </c>
       <c r="M154" s="1"/>
     </row>
-    <row r="155" spans="1:13">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>152</v>
       </c>
@@ -9189,7 +9173,7 @@
       </c>
       <c r="M155" s="1"/>
     </row>
-    <row r="156" spans="1:13">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>153</v>
       </c>
@@ -9224,7 +9208,7 @@
       </c>
       <c r="M156" s="1"/>
     </row>
-    <row r="157" spans="1:13">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>154</v>
       </c>
@@ -9259,7 +9243,7 @@
       </c>
       <c r="M157" s="1"/>
     </row>
-    <row r="158" spans="1:13">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>155</v>
       </c>
@@ -9294,7 +9278,7 @@
       </c>
       <c r="M158" s="1"/>
     </row>
-    <row r="159" spans="1:13">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>156</v>
       </c>
@@ -9329,7 +9313,7 @@
       </c>
       <c r="M159" s="1"/>
     </row>
-    <row r="160" spans="1:13">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>157</v>
       </c>
@@ -9364,7 +9348,7 @@
       </c>
       <c r="M160" s="1"/>
     </row>
-    <row r="161" spans="1:13">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>158</v>
       </c>
@@ -9399,7 +9383,7 @@
       </c>
       <c r="M161" s="1"/>
     </row>
-    <row r="162" spans="1:13">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>159</v>
       </c>
@@ -9434,7 +9418,7 @@
       </c>
       <c r="M162" s="1"/>
     </row>
-    <row r="163" spans="1:13">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>160</v>
       </c>
@@ -9469,7 +9453,7 @@
       </c>
       <c r="M163" s="1"/>
     </row>
-    <row r="164" spans="1:13">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>161</v>
       </c>
@@ -9504,7 +9488,7 @@
       </c>
       <c r="M164" s="1"/>
     </row>
-    <row r="165" spans="1:13">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>162</v>
       </c>
@@ -9539,7 +9523,7 @@
       </c>
       <c r="M165" s="1"/>
     </row>
-    <row r="166" spans="1:13">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>163</v>
       </c>
@@ -9574,7 +9558,7 @@
       </c>
       <c r="M166" s="1"/>
     </row>
-    <row r="167" spans="1:13">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>164</v>
       </c>
@@ -9609,7 +9593,7 @@
       </c>
       <c r="M167" s="1"/>
     </row>
-    <row r="168" spans="1:13">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>165</v>
       </c>
@@ -9644,7 +9628,7 @@
       </c>
       <c r="M168" s="1"/>
     </row>
-    <row r="169" spans="1:13">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>166</v>
       </c>
@@ -9679,7 +9663,7 @@
       </c>
       <c r="M169" s="1"/>
     </row>
-    <row r="170" spans="1:13">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>167</v>
       </c>
@@ -9714,7 +9698,7 @@
       </c>
       <c r="M170" s="1"/>
     </row>
-    <row r="171" spans="1:13">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>168</v>
       </c>
@@ -9749,7 +9733,7 @@
       </c>
       <c r="M171" s="1"/>
     </row>
-    <row r="172" spans="1:13">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>169</v>
       </c>
@@ -9784,7 +9768,7 @@
       </c>
       <c r="M172" s="1"/>
     </row>
-    <row r="173" spans="1:13">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>170</v>
       </c>
@@ -9819,7 +9803,7 @@
       </c>
       <c r="M173" s="1"/>
     </row>
-    <row r="174" spans="1:13">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>171</v>
       </c>
@@ -9854,7 +9838,7 @@
       </c>
       <c r="M174" s="1"/>
     </row>
-    <row r="175" spans="1:13">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>172</v>
       </c>
@@ -9889,7 +9873,7 @@
       </c>
       <c r="M175" s="1"/>
     </row>
-    <row r="176" spans="1:13">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>173</v>
       </c>
@@ -9924,7 +9908,7 @@
       </c>
       <c r="M176" s="1"/>
     </row>
-    <row r="177" spans="1:13">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>174</v>
       </c>
@@ -9959,7 +9943,7 @@
       </c>
       <c r="M177" s="1"/>
     </row>
-    <row r="178" spans="1:13">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>175</v>
       </c>
@@ -9994,7 +9978,7 @@
       </c>
       <c r="M178" s="1"/>
     </row>
-    <row r="179" spans="1:13">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>176</v>
       </c>
@@ -10029,7 +10013,7 @@
       </c>
       <c r="M179" s="1"/>
     </row>
-    <row r="180" spans="1:13">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>177</v>
       </c>
@@ -10064,7 +10048,7 @@
       </c>
       <c r="M180" s="1"/>
     </row>
-    <row r="181" spans="1:13">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>178</v>
       </c>
@@ -10099,7 +10083,7 @@
       </c>
       <c r="M181" s="1"/>
     </row>
-    <row r="182" spans="1:13">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>179</v>
       </c>
@@ -10134,7 +10118,7 @@
       </c>
       <c r="M182" s="1"/>
     </row>
-    <row r="183" spans="1:13">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>180</v>
       </c>
@@ -10169,7 +10153,7 @@
       </c>
       <c r="M183" s="1"/>
     </row>
-    <row r="184" spans="1:13">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>181</v>
       </c>
@@ -10204,7 +10188,7 @@
       </c>
       <c r="M184" s="1"/>
     </row>
-    <row r="185" spans="1:13">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>182</v>
       </c>
@@ -10239,7 +10223,7 @@
       </c>
       <c r="M185" s="1"/>
     </row>
-    <row r="186" spans="1:13">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>183</v>
       </c>
@@ -10274,7 +10258,7 @@
       </c>
       <c r="M186" s="1"/>
     </row>
-    <row r="187" spans="1:13">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>184</v>
       </c>
@@ -10309,7 +10293,7 @@
       </c>
       <c r="M187" s="1"/>
     </row>
-    <row r="188" spans="1:13">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>185</v>
       </c>
@@ -10344,7 +10328,7 @@
       </c>
       <c r="M188" s="1"/>
     </row>
-    <row r="189" spans="1:13">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>186</v>
       </c>
@@ -10379,7 +10363,7 @@
       </c>
       <c r="M189" s="1"/>
     </row>
-    <row r="190" spans="1:13">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>187</v>
       </c>
@@ -10414,7 +10398,7 @@
       </c>
       <c r="M190" s="1"/>
     </row>
-    <row r="191" spans="1:13">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>188</v>
       </c>
@@ -10449,7 +10433,7 @@
       </c>
       <c r="M191" s="1"/>
     </row>
-    <row r="192" spans="1:13">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>189</v>
       </c>
@@ -10484,7 +10468,7 @@
       </c>
       <c r="M192" s="1"/>
     </row>
-    <row r="193" spans="1:13">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>190</v>
       </c>
@@ -10519,7 +10503,7 @@
       </c>
       <c r="M193" s="1"/>
     </row>
-    <row r="194" spans="1:13">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>191</v>
       </c>
@@ -10554,7 +10538,7 @@
       </c>
       <c r="M194" s="1"/>
     </row>
-    <row r="195" spans="1:13">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>192</v>
       </c>
@@ -10589,7 +10573,7 @@
       </c>
       <c r="M195" s="1"/>
     </row>
-    <row r="196" spans="1:13">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>193</v>
       </c>
@@ -10624,7 +10608,7 @@
       </c>
       <c r="M196" s="1"/>
     </row>
-    <row r="197" spans="1:13">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>194</v>
       </c>
@@ -10659,7 +10643,7 @@
       </c>
       <c r="M197" s="1"/>
     </row>
-    <row r="198" spans="1:13">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>195</v>
       </c>
@@ -10694,7 +10678,7 @@
       </c>
       <c r="M198" s="1"/>
     </row>
-    <row r="199" spans="1:13">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>196</v>
       </c>
@@ -10729,7 +10713,7 @@
       </c>
       <c r="M199" s="1"/>
     </row>
-    <row r="200" spans="1:13">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>197</v>
       </c>
@@ -10764,7 +10748,7 @@
       </c>
       <c r="M200" s="1"/>
     </row>
-    <row r="201" spans="1:13">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>198</v>
       </c>
@@ -10799,7 +10783,7 @@
       </c>
       <c r="M201" s="1"/>
     </row>
-    <row r="202" spans="1:13">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>199</v>
       </c>
@@ -10834,7 +10818,7 @@
       </c>
       <c r="M202" s="1"/>
     </row>
-    <row r="203" spans="1:13">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>200</v>
       </c>
@@ -10869,7 +10853,7 @@
       </c>
       <c r="M203" s="1"/>
     </row>
-    <row r="204" spans="1:13">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>201</v>
       </c>
@@ -10904,7 +10888,7 @@
       </c>
       <c r="M204" s="1"/>
     </row>
-    <row r="205" spans="1:13">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>202</v>
       </c>
@@ -10939,7 +10923,7 @@
       </c>
       <c r="M205" s="1"/>
     </row>
-    <row r="206" spans="1:13">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>203</v>
       </c>
@@ -10974,7 +10958,7 @@
       </c>
       <c r="M206" s="1"/>
     </row>
-    <row r="207" spans="1:13">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>204</v>
       </c>
@@ -11009,7 +10993,7 @@
       </c>
       <c r="M207" s="1"/>
     </row>
-    <row r="208" spans="1:13">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>205</v>
       </c>
@@ -11044,7 +11028,7 @@
       </c>
       <c r="M208" s="1"/>
     </row>
-    <row r="209" spans="1:13">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>206</v>
       </c>
@@ -11079,7 +11063,7 @@
       </c>
       <c r="M209" s="1"/>
     </row>
-    <row r="210" spans="1:13">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>207</v>
       </c>
@@ -11114,7 +11098,7 @@
       </c>
       <c r="M210" s="1"/>
     </row>
-    <row r="211" spans="1:13">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>208</v>
       </c>
@@ -11149,7 +11133,7 @@
       </c>
       <c r="M211" s="1"/>
     </row>
-    <row r="212" spans="1:13">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>209</v>
       </c>
@@ -11184,7 +11168,7 @@
       </c>
       <c r="M212" s="1"/>
     </row>
-    <row r="213" spans="1:13">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>210</v>
       </c>
@@ -11219,7 +11203,7 @@
       </c>
       <c r="M213" s="1"/>
     </row>
-    <row r="214" spans="1:13">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>211</v>
       </c>
@@ -11254,7 +11238,7 @@
       </c>
       <c r="M214" s="1"/>
     </row>
-    <row r="215" spans="1:13">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>212</v>
       </c>
@@ -11289,7 +11273,7 @@
       </c>
       <c r="M215" s="1"/>
     </row>
-    <row r="216" spans="1:13">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>213</v>
       </c>
@@ -11324,7 +11308,7 @@
       </c>
       <c r="M216" s="1"/>
     </row>
-    <row r="217" spans="1:13">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>214</v>
       </c>
@@ -11359,7 +11343,7 @@
       </c>
       <c r="M217" s="1"/>
     </row>
-    <row r="218" spans="1:13">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>215</v>
       </c>
@@ -11394,7 +11378,7 @@
       </c>
       <c r="M218" s="1"/>
     </row>
-    <row r="219" spans="1:13">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>216</v>
       </c>
@@ -11429,7 +11413,7 @@
       </c>
       <c r="M219" s="1"/>
     </row>
-    <row r="220" spans="1:13">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>217</v>
       </c>
@@ -11464,7 +11448,7 @@
       </c>
       <c r="M220" s="1"/>
     </row>
-    <row r="221" spans="1:13">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>218</v>
       </c>
@@ -11499,7 +11483,7 @@
       </c>
       <c r="M221" s="1"/>
     </row>
-    <row r="222" spans="1:13">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>219</v>
       </c>
@@ -11534,7 +11518,7 @@
       </c>
       <c r="M222" s="1"/>
     </row>
-    <row r="223" spans="1:13">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>220</v>
       </c>
@@ -11569,7 +11553,7 @@
       </c>
       <c r="M223" s="1"/>
     </row>
-    <row r="224" spans="1:13">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>221</v>
       </c>
@@ -11604,7 +11588,7 @@
       </c>
       <c r="M224" s="1"/>
     </row>
-    <row r="225" spans="1:13">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>222</v>
       </c>
@@ -11639,7 +11623,7 @@
       </c>
       <c r="M225" s="1"/>
     </row>
-    <row r="226" spans="1:13">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>223</v>
       </c>
@@ -11674,7 +11658,7 @@
       </c>
       <c r="M226" s="1"/>
     </row>
-    <row r="227" spans="1:13">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>224</v>
       </c>
@@ -11709,7 +11693,7 @@
       </c>
       <c r="M227" s="1"/>
     </row>
-    <row r="228" spans="1:13">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>225</v>
       </c>
@@ -11744,7 +11728,7 @@
       </c>
       <c r="M228" s="1"/>
     </row>
-    <row r="229" spans="1:13">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>226</v>
       </c>
@@ -11779,7 +11763,7 @@
       </c>
       <c r="M229" s="1"/>
     </row>
-    <row r="230" spans="1:13">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>227</v>
       </c>
@@ -11814,7 +11798,7 @@
       </c>
       <c r="M230" s="1"/>
     </row>
-    <row r="231" spans="1:13">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>228</v>
       </c>
@@ -11849,7 +11833,7 @@
       </c>
       <c r="M231" s="1"/>
     </row>
-    <row r="232" spans="1:13">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>229</v>
       </c>
@@ -11884,7 +11868,7 @@
       </c>
       <c r="M232" s="1"/>
     </row>
-    <row r="233" spans="1:13">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>230</v>
       </c>
@@ -11919,7 +11903,7 @@
       </c>
       <c r="M233" s="1"/>
     </row>
-    <row r="234" spans="1:13">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>231</v>
       </c>
@@ -11954,7 +11938,7 @@
       </c>
       <c r="M234" s="1"/>
     </row>
-    <row r="235" spans="1:13">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>232</v>
       </c>
@@ -11989,7 +11973,7 @@
       </c>
       <c r="M235" s="1"/>
     </row>
-    <row r="236" spans="1:13">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>233</v>
       </c>
@@ -12024,7 +12008,7 @@
       </c>
       <c r="M236" s="1"/>
     </row>
-    <row r="237" spans="1:13">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>234</v>
       </c>
@@ -12059,7 +12043,7 @@
       </c>
       <c r="M237" s="1"/>
     </row>
-    <row r="238" spans="1:13">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>235</v>
       </c>
@@ -12094,7 +12078,7 @@
       </c>
       <c r="M238" s="1"/>
     </row>
-    <row r="239" spans="1:13">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>236</v>
       </c>
@@ -12129,7 +12113,7 @@
       </c>
       <c r="M239" s="1"/>
     </row>
-    <row r="240" spans="1:13">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>237</v>
       </c>
@@ -12164,7 +12148,7 @@
       </c>
       <c r="M240" s="1"/>
     </row>
-    <row r="241" spans="1:13">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>238</v>
       </c>
@@ -12199,7 +12183,7 @@
       </c>
       <c r="M241" s="1"/>
     </row>
-    <row r="242" spans="1:13">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>239</v>
       </c>
@@ -12234,7 +12218,7 @@
       </c>
       <c r="M242" s="1"/>
     </row>
-    <row r="243" spans="1:13">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>240</v>
       </c>
@@ -12269,7 +12253,7 @@
       </c>
       <c r="M243" s="1"/>
     </row>
-    <row r="244" spans="1:13">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>241</v>
       </c>
@@ -12304,7 +12288,7 @@
       </c>
       <c r="M244" s="1"/>
     </row>
-    <row r="245" spans="1:13">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>242</v>
       </c>
@@ -12339,7 +12323,7 @@
       </c>
       <c r="M245" s="1"/>
     </row>
-    <row r="246" spans="1:13">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>243</v>
       </c>
@@ -12374,7 +12358,7 @@
       </c>
       <c r="M246" s="1"/>
     </row>
-    <row r="247" spans="1:13">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>244</v>
       </c>
@@ -12409,7 +12393,7 @@
       </c>
       <c r="M247" s="1"/>
     </row>
-    <row r="248" spans="1:13">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>245</v>
       </c>
@@ -12444,7 +12428,7 @@
       </c>
       <c r="M248" s="1"/>
     </row>
-    <row r="249" spans="1:13">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>246</v>
       </c>
@@ -12479,7 +12463,7 @@
       </c>
       <c r="M249" s="1"/>
     </row>
-    <row r="250" spans="1:13">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>247</v>
       </c>
@@ -12514,7 +12498,7 @@
       </c>
       <c r="M250" s="1"/>
     </row>
-    <row r="251" spans="1:13">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>248</v>
       </c>
@@ -12549,7 +12533,7 @@
       </c>
       <c r="M251" s="1"/>
     </row>
-    <row r="252" spans="1:13">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>249</v>
       </c>
@@ -12584,7 +12568,7 @@
       </c>
       <c r="M252" s="1"/>
     </row>
-    <row r="253" spans="1:13">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>250</v>
       </c>
@@ -12619,7 +12603,7 @@
       </c>
       <c r="M253" s="1"/>
     </row>
-    <row r="254" spans="1:13">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>251</v>
       </c>
@@ -12654,7 +12638,7 @@
       </c>
       <c r="M254" s="1"/>
     </row>
-    <row r="255" spans="1:13">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>252</v>
       </c>
@@ -12689,7 +12673,7 @@
       </c>
       <c r="M255" s="1"/>
     </row>
-    <row r="256" spans="1:13">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>253</v>
       </c>
@@ -12724,7 +12708,7 @@
       </c>
       <c r="M256" s="1"/>
     </row>
-    <row r="257" spans="1:13">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>254</v>
       </c>
@@ -12759,7 +12743,7 @@
       </c>
       <c r="M257" s="1"/>
     </row>
-    <row r="258" spans="1:13">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>255</v>
       </c>
@@ -12794,7 +12778,7 @@
       </c>
       <c r="M258" s="1"/>
     </row>
-    <row r="259" spans="1:13">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>256</v>
       </c>
@@ -12829,7 +12813,7 @@
       </c>
       <c r="M259" s="1"/>
     </row>
-    <row r="260" spans="1:13">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>257</v>
       </c>
@@ -12864,7 +12848,7 @@
       </c>
       <c r="M260" s="1"/>
     </row>
-    <row r="261" spans="1:13">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>258</v>
       </c>
@@ -12899,7 +12883,7 @@
       </c>
       <c r="M261" s="1"/>
     </row>
-    <row r="262" spans="1:13">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>259</v>
       </c>
@@ -12934,7 +12918,7 @@
       </c>
       <c r="M262" s="1"/>
     </row>
-    <row r="263" spans="1:13">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>260</v>
       </c>
@@ -12969,7 +12953,7 @@
       </c>
       <c r="M263" s="1"/>
     </row>
-    <row r="264" spans="1:13">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>261</v>
       </c>
@@ -13004,7 +12988,7 @@
       </c>
       <c r="M264" s="1"/>
     </row>
-    <row r="265" spans="1:13">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>262</v>
       </c>
@@ -13039,7 +13023,7 @@
       </c>
       <c r="M265" s="1"/>
     </row>
-    <row r="266" spans="1:13">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>263</v>
       </c>
@@ -13074,7 +13058,7 @@
       </c>
       <c r="M266" s="1"/>
     </row>
-    <row r="267" spans="1:13">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>264</v>
       </c>
@@ -13109,7 +13093,7 @@
       </c>
       <c r="M267" s="1"/>
     </row>
-    <row r="268" spans="1:13">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>265</v>
       </c>
@@ -13144,7 +13128,7 @@
       </c>
       <c r="M268" s="1"/>
     </row>
-    <row r="269" spans="1:13">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>266</v>
       </c>
@@ -13179,7 +13163,7 @@
       </c>
       <c r="M269" s="1"/>
     </row>
-    <row r="270" spans="1:13">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>267</v>
       </c>
@@ -13214,7 +13198,7 @@
       </c>
       <c r="M270" s="1"/>
     </row>
-    <row r="271" spans="1:13">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>268</v>
       </c>
@@ -13249,7 +13233,7 @@
       </c>
       <c r="M271" s="1"/>
     </row>
-    <row r="272" spans="1:13">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>269</v>
       </c>
@@ -13284,7 +13268,7 @@
       </c>
       <c r="M272" s="1"/>
     </row>
-    <row r="273" spans="1:13">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>270</v>
       </c>
@@ -13319,7 +13303,7 @@
       </c>
       <c r="M273" s="1"/>
     </row>
-    <row r="274" spans="1:13">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>271</v>
       </c>
@@ -13354,7 +13338,7 @@
       </c>
       <c r="M274" s="1"/>
     </row>
-    <row r="275" spans="1:13">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>272</v>
       </c>
@@ -13389,7 +13373,7 @@
       </c>
       <c r="M275" s="1"/>
     </row>
-    <row r="276" spans="1:13">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>273</v>
       </c>
@@ -13424,7 +13408,7 @@
       </c>
       <c r="M276" s="1"/>
     </row>
-    <row r="277" spans="1:13">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>274</v>
       </c>
@@ -13459,7 +13443,7 @@
       </c>
       <c r="M277" s="1"/>
     </row>
-    <row r="278" spans="1:13">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>275</v>
       </c>
@@ -13494,7 +13478,7 @@
       </c>
       <c r="M278" s="1"/>
     </row>
-    <row r="279" spans="1:13">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>276</v>
       </c>
@@ -13529,7 +13513,7 @@
       </c>
       <c r="M279" s="1"/>
     </row>
-    <row r="280" spans="1:13">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>277</v>
       </c>
@@ -13564,7 +13548,7 @@
       </c>
       <c r="M280" s="1"/>
     </row>
-    <row r="281" spans="1:13">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>278</v>
       </c>
@@ -13599,7 +13583,7 @@
       </c>
       <c r="M281" s="1"/>
     </row>
-    <row r="282" spans="1:13">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>279</v>
       </c>
@@ -13634,7 +13618,7 @@
       </c>
       <c r="M282" s="1"/>
     </row>
-    <row r="283" spans="1:13">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>280</v>
       </c>
@@ -13669,7 +13653,7 @@
       </c>
       <c r="M283" s="1"/>
     </row>
-    <row r="284" spans="1:13">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>281</v>
       </c>
@@ -13704,7 +13688,7 @@
       </c>
       <c r="M284" s="1"/>
     </row>
-    <row r="285" spans="1:13">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>282</v>
       </c>
@@ -13739,7 +13723,7 @@
       </c>
       <c r="M285" s="1"/>
     </row>
-    <row r="286" spans="1:13">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>283</v>
       </c>
@@ -13774,7 +13758,7 @@
       </c>
       <c r="M286" s="1"/>
     </row>
-    <row r="287" spans="1:13">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>284</v>
       </c>
@@ -13809,7 +13793,7 @@
       </c>
       <c r="M287" s="1"/>
     </row>
-    <row r="288" spans="1:13">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>285</v>
       </c>
@@ -13844,7 +13828,7 @@
       </c>
       <c r="M288" s="1"/>
     </row>
-    <row r="289" spans="1:13">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>286</v>
       </c>
@@ -13879,7 +13863,7 @@
       </c>
       <c r="M289" s="1"/>
     </row>
-    <row r="290" spans="1:13">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>287</v>
       </c>
@@ -13914,7 +13898,7 @@
       </c>
       <c r="M290" s="1"/>
     </row>
-    <row r="291" spans="1:13">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>288</v>
       </c>
@@ -13949,7 +13933,7 @@
       </c>
       <c r="M291" s="1"/>
     </row>
-    <row r="292" spans="1:13">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>289</v>
       </c>
@@ -13984,7 +13968,7 @@
       </c>
       <c r="M292" s="1"/>
     </row>
-    <row r="293" spans="1:13">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>290</v>
       </c>
@@ -14019,7 +14003,7 @@
       </c>
       <c r="M293" s="1"/>
     </row>
-    <row r="294" spans="1:13">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>291</v>
       </c>
@@ -14054,7 +14038,7 @@
       </c>
       <c r="M294" s="1"/>
     </row>
-    <row r="295" spans="1:13">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>292</v>
       </c>
@@ -14089,7 +14073,7 @@
       </c>
       <c r="M295" s="1"/>
     </row>
-    <row r="296" spans="1:13">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>293</v>
       </c>
@@ -14124,7 +14108,7 @@
       </c>
       <c r="M296" s="1"/>
     </row>
-    <row r="297" spans="1:13">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>294</v>
       </c>
@@ -14159,7 +14143,7 @@
       </c>
       <c r="M297" s="1"/>
     </row>
-    <row r="298" spans="1:13">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>295</v>
       </c>
@@ -14194,7 +14178,7 @@
       </c>
       <c r="M298" s="1"/>
     </row>
-    <row r="299" spans="1:13">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>296</v>
       </c>
@@ -14229,7 +14213,7 @@
       </c>
       <c r="M299" s="1"/>
     </row>
-    <row r="300" spans="1:13">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>297</v>
       </c>
@@ -14264,7 +14248,7 @@
       </c>
       <c r="M300" s="1"/>
     </row>
-    <row r="301" spans="1:13">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>298</v>
       </c>
@@ -14299,7 +14283,7 @@
       </c>
       <c r="M301" s="1"/>
     </row>
-    <row r="302" spans="1:13">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>299</v>
       </c>
@@ -14334,7 +14318,7 @@
       </c>
       <c r="M302" s="1"/>
     </row>
-    <row r="303" spans="1:13">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>300</v>
       </c>
@@ -14369,7 +14353,7 @@
       </c>
       <c r="M303" s="1"/>
     </row>
-    <row r="304" spans="1:13">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>301</v>
       </c>
@@ -14404,7 +14388,7 @@
       </c>
       <c r="M304" s="1"/>
     </row>
-    <row r="305" spans="1:13">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>302</v>
       </c>
@@ -14439,7 +14423,7 @@
       </c>
       <c r="M305" s="1"/>
     </row>
-    <row r="306" spans="1:13">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>303</v>
       </c>
@@ -14474,7 +14458,7 @@
       </c>
       <c r="M306" s="1"/>
     </row>
-    <row r="307" spans="1:13">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>304</v>
       </c>
@@ -14509,7 +14493,7 @@
       </c>
       <c r="M307" s="1"/>
     </row>
-    <row r="308" spans="1:13">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>305</v>
       </c>
@@ -14544,7 +14528,7 @@
       </c>
       <c r="M308" s="1"/>
     </row>
-    <row r="309" spans="1:13">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>306</v>
       </c>
@@ -14579,7 +14563,7 @@
       </c>
       <c r="M309" s="1"/>
     </row>
-    <row r="310" spans="1:13">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>307</v>
       </c>
@@ -14614,7 +14598,7 @@
       </c>
       <c r="M310" s="1"/>
     </row>
-    <row r="311" spans="1:13">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>308</v>
       </c>
@@ -14649,7 +14633,7 @@
       </c>
       <c r="M311" s="1"/>
     </row>
-    <row r="312" spans="1:13">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>309</v>
       </c>
@@ -14684,7 +14668,7 @@
       </c>
       <c r="M312" s="1"/>
     </row>
-    <row r="313" spans="1:13">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>310</v>
       </c>
@@ -14721,7 +14705,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="314" spans="1:13">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>311</v>
       </c>
@@ -14756,7 +14740,7 @@
       </c>
       <c r="M314" s="1"/>
     </row>
-    <row r="315" spans="1:13">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>312</v>
       </c>
@@ -14791,7 +14775,7 @@
       </c>
       <c r="M315" s="1"/>
     </row>
-    <row r="316" spans="1:13">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>313</v>
       </c>
@@ -14826,7 +14810,7 @@
       </c>
       <c r="M316" s="1"/>
     </row>
-    <row r="317" spans="1:13">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>314</v>
       </c>
@@ -14861,7 +14845,7 @@
       </c>
       <c r="M317" s="1"/>
     </row>
-    <row r="318" spans="1:13">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>315</v>
       </c>
@@ -14896,7 +14880,7 @@
       </c>
       <c r="M318" s="1"/>
     </row>
-    <row r="319" spans="1:13">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>316</v>
       </c>
@@ -14931,7 +14915,7 @@
       </c>
       <c r="M319" s="1"/>
     </row>
-    <row r="320" spans="1:13">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>317</v>
       </c>
@@ -14966,7 +14950,7 @@
       </c>
       <c r="M320" s="1"/>
     </row>
-    <row r="321" spans="1:13">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>318</v>
       </c>
@@ -15001,7 +14985,7 @@
       </c>
       <c r="M321" s="1"/>
     </row>
-    <row r="322" spans="1:13">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>319</v>
       </c>
@@ -15036,7 +15020,7 @@
       </c>
       <c r="M322" s="1"/>
     </row>
-    <row r="323" spans="1:13">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>320</v>
       </c>
@@ -15071,7 +15055,7 @@
       </c>
       <c r="M323" s="1"/>
     </row>
-    <row r="324" spans="1:13">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>321</v>
       </c>
@@ -15106,7 +15090,7 @@
       </c>
       <c r="M324" s="1"/>
     </row>
-    <row r="325" spans="1:13">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>322</v>
       </c>
@@ -15141,7 +15125,7 @@
       </c>
       <c r="M325" s="1"/>
     </row>
-    <row r="326" spans="1:13">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>323</v>
       </c>
@@ -15176,7 +15160,7 @@
       </c>
       <c r="M326" s="1"/>
     </row>
-    <row r="327" spans="1:13">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>324</v>
       </c>
@@ -15211,7 +15195,7 @@
       </c>
       <c r="M327" s="1"/>
     </row>
-    <row r="328" spans="1:13">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>325</v>
       </c>
@@ -15246,7 +15230,7 @@
       </c>
       <c r="M328" s="1"/>
     </row>
-    <row r="329" spans="1:13">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>326</v>
       </c>
@@ -15281,7 +15265,7 @@
       </c>
       <c r="M329" s="1"/>
     </row>
-    <row r="330" spans="1:13">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>327</v>
       </c>
@@ -15316,7 +15300,7 @@
       </c>
       <c r="M330" s="1"/>
     </row>
-    <row r="331" spans="1:13">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>328</v>
       </c>
@@ -15351,7 +15335,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="332" spans="1:13">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>329</v>
       </c>
@@ -15386,7 +15370,7 @@
       </c>
       <c r="M332" s="1"/>
     </row>
-    <row r="333" spans="1:13">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>330</v>
       </c>
@@ -15421,7 +15405,7 @@
       </c>
       <c r="M333" s="1"/>
     </row>
-    <row r="334" spans="1:13">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>331</v>
       </c>
@@ -15456,7 +15440,7 @@
       </c>
       <c r="M334" s="1"/>
     </row>
-    <row r="335" spans="1:13">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>332</v>
       </c>
@@ -15491,7 +15475,7 @@
       </c>
       <c r="M335" s="1"/>
     </row>
-    <row r="336" spans="1:13">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>333</v>
       </c>
@@ -15526,7 +15510,7 @@
       </c>
       <c r="M336" s="1"/>
     </row>
-    <row r="337" spans="1:13">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>334</v>
       </c>
@@ -15561,7 +15545,7 @@
       </c>
       <c r="M337" s="1"/>
     </row>
-    <row r="338" spans="1:13">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>335</v>
       </c>
@@ -15596,7 +15580,7 @@
       </c>
       <c r="M338" s="1"/>
     </row>
-    <row r="339" spans="1:13">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>336</v>
       </c>
@@ -15631,7 +15615,7 @@
       </c>
       <c r="M339" s="1"/>
     </row>
-    <row r="340" spans="1:13">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>337</v>
       </c>
@@ -15666,7 +15650,7 @@
       </c>
       <c r="M340" s="1"/>
     </row>
-    <row r="341" spans="1:13">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>338</v>
       </c>
@@ -15701,7 +15685,7 @@
       </c>
       <c r="M341" s="1"/>
     </row>
-    <row r="342" spans="1:13">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>339</v>
       </c>
@@ -15738,7 +15722,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="343" spans="1:13">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>340</v>
       </c>
@@ -15775,7 +15759,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="344" spans="1:13">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>341</v>
       </c>
@@ -15812,7 +15796,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="345" spans="1:13">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>342</v>
       </c>
@@ -15847,7 +15831,7 @@
       </c>
       <c r="M345" s="1"/>
     </row>
-    <row r="346" spans="1:13">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>343</v>
       </c>
@@ -15884,7 +15868,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="347" spans="1:13">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>344</v>
       </c>
@@ -15919,42 +15903,42 @@
       </c>
       <c r="M347" s="11"/>
     </row>
-    <row r="348" spans="1:13" ht="30">
+    <row r="348" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="8">
         <v>345</v>
       </c>
-      <c r="B348" s="19">
+      <c r="B348" s="12">
         <v>46226</v>
       </c>
-      <c r="C348" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D348" s="20" t="s">
+      <c r="C348" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D348" s="13" t="s">
         <v>981</v>
       </c>
-      <c r="E348" s="20"/>
-      <c r="F348" s="20" t="s">
+      <c r="E348" s="13"/>
+      <c r="F348" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="G348" s="20" t="s">
+      <c r="G348" s="13" t="s">
         <v>758</v>
       </c>
-      <c r="H348" s="21" t="s">
+      <c r="H348" s="14" t="s">
         <v>982</v>
       </c>
-      <c r="I348" s="21" t="s">
+      <c r="I348" s="14" t="s">
         <v>983</v>
       </c>
-      <c r="J348" s="22" t="s">
+      <c r="J348" s="21" t="s">
         <v>984</v>
       </c>
-      <c r="K348" s="22"/>
-      <c r="L348" s="20" t="s">
+      <c r="K348" s="19"/>
+      <c r="L348" s="13" t="s">
         <v>509</v>
       </c>
-      <c r="M348" s="20"/>
-    </row>
-    <row r="349" spans="1:13" ht="75" customHeight="1">
+      <c r="M348" s="13"/>
+    </row>
+    <row r="349" spans="1:13" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="9">
         <v>346</v>
       </c>
@@ -15964,10 +15948,10 @@
       <c r="C349" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D349" s="13" t="s">
+      <c r="D349" s="16" t="s">
         <v>985</v>
       </c>
-      <c r="E349" s="13"/>
+      <c r="E349" s="17"/>
       <c r="F349" s="7" t="s">
         <v>986</v>
       </c>
@@ -15980,121 +15964,121 @@
       <c r="I349" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="J349" s="13" t="s">
+      <c r="J349" s="16" t="s">
         <v>988</v>
       </c>
-      <c r="K349" s="12"/>
+      <c r="K349" s="17"/>
       <c r="L349" s="6" t="s">
         <v>509</v>
       </c>
       <c r="M349" s="6"/>
     </row>
-    <row r="350" spans="1:13" ht="60.75" customHeight="1">
-      <c r="A350" s="20">
+    <row r="350" spans="1:13" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A350" s="13">
         <v>347</v>
       </c>
-      <c r="B350" s="23">
+      <c r="B350" s="15">
         <v>46226</v>
       </c>
-      <c r="C350" s="20" t="s">
+      <c r="C350" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D350" s="24" t="s">
+      <c r="D350" s="18" t="s">
         <v>989</v>
       </c>
-      <c r="E350" s="25"/>
-      <c r="F350" s="20" t="s">
+      <c r="E350" s="19"/>
+      <c r="F350" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="G350" s="20" t="s">
+      <c r="G350" s="13" t="s">
         <v>688</v>
       </c>
-      <c r="H350" s="21" t="s">
+      <c r="H350" s="14" t="s">
         <v>990</v>
       </c>
-      <c r="I350" s="20" t="s">
+      <c r="I350" s="13" t="s">
         <v>901</v>
       </c>
-      <c r="J350" s="24" t="s">
+      <c r="J350" s="18" t="s">
         <v>991</v>
       </c>
-      <c r="K350" s="26"/>
-      <c r="L350" s="20" t="s">
+      <c r="K350" s="19"/>
+      <c r="L350" s="13" t="s">
         <v>509</v>
       </c>
-      <c r="M350" s="20"/>
-    </row>
-    <row r="351" spans="1:13" ht="45.75" customHeight="1">
-      <c r="A351" s="20">
+      <c r="M350" s="13"/>
+    </row>
+    <row r="351" spans="1:13" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A351" s="13">
         <v>348</v>
       </c>
-      <c r="B351" s="19">
+      <c r="B351" s="12">
         <v>46226</v>
       </c>
-      <c r="C351" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D351" s="24" t="s">
+      <c r="C351" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D351" s="18" t="s">
         <v>992</v>
       </c>
-      <c r="E351" s="25"/>
-      <c r="F351" s="20" t="s">
+      <c r="E351" s="19"/>
+      <c r="F351" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="G351" s="20" t="s">
+      <c r="G351" s="13" t="s">
         <v>994</v>
       </c>
-      <c r="H351" s="20" t="s">
+      <c r="H351" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="I351" s="20" t="s">
+      <c r="I351" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J351" s="27" t="s">
+      <c r="J351" s="21" t="s">
         <v>995</v>
       </c>
-      <c r="K351" s="26"/>
-      <c r="L351" s="20" t="s">
+      <c r="K351" s="19"/>
+      <c r="L351" s="13" t="s">
         <v>509</v>
       </c>
-      <c r="M351" s="20"/>
-    </row>
-    <row r="352" spans="1:13" ht="46.5" customHeight="1">
-      <c r="A352" s="20">
+      <c r="M351" s="13"/>
+    </row>
+    <row r="352" spans="1:13" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A352" s="13">
         <v>349</v>
       </c>
-      <c r="B352" s="19">
+      <c r="B352" s="12">
         <v>46219</v>
       </c>
-      <c r="C352" s="20" t="s">
+      <c r="C352" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="D352" s="24" t="s">
+      <c r="D352" s="18" t="s">
         <v>996</v>
       </c>
-      <c r="E352" s="26"/>
-      <c r="F352" s="20" t="s">
+      <c r="E352" s="19"/>
+      <c r="F352" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="G352" s="21" t="s">
+      <c r="G352" s="14" t="s">
         <v>997</v>
       </c>
-      <c r="H352" s="20" t="s">
+      <c r="H352" s="13" t="s">
         <v>993</v>
       </c>
-      <c r="I352" s="20" t="s">
+      <c r="I352" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J352" s="27" t="s">
+      <c r="J352" s="21" t="s">
         <v>995</v>
       </c>
-      <c r="K352" s="26"/>
-      <c r="L352" s="20" t="s">
+      <c r="K352" s="19"/>
+      <c r="L352" s="13" t="s">
         <v>509</v>
       </c>
-      <c r="M352" s="20"/>
-    </row>
-    <row r="353" spans="1:13" ht="76.5" customHeight="1">
+      <c r="M352" s="13"/>
+    </row>
+    <row r="353" spans="1:13" ht="76.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
         <v>350</v>
       </c>
@@ -16104,10 +16088,10 @@
       <c r="C353" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D353" s="13" t="s">
+      <c r="D353" s="16" t="s">
         <v>998</v>
       </c>
-      <c r="E353" s="13"/>
+      <c r="E353" s="17"/>
       <c r="F353" s="6" t="s">
         <v>153</v>
       </c>
@@ -16120,16 +16104,16 @@
       <c r="I353" s="6" t="s">
         <v>917</v>
       </c>
-      <c r="J353" s="17" t="s">
+      <c r="J353" s="20" t="s">
         <v>999</v>
       </c>
-      <c r="K353" s="18"/>
+      <c r="K353" s="17"/>
       <c r="L353" s="6" t="s">
         <v>509</v>
       </c>
       <c r="M353" s="6"/>
     </row>
-    <row r="354" spans="1:13">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
         <v>351</v>
       </c>
@@ -16139,10 +16123,10 @@
       <c r="C354" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D354" s="13" t="s">
+      <c r="D354" s="16" t="s">
         <v>1000</v>
       </c>
-      <c r="E354" s="13"/>
+      <c r="E354" s="17"/>
       <c r="F354" s="6" t="s">
         <v>153</v>
       </c>
@@ -16155,16 +16139,16 @@
       <c r="I354" s="6" t="s">
         <v>917</v>
       </c>
-      <c r="J354" s="17" t="s">
+      <c r="J354" s="20" t="s">
         <v>1001</v>
       </c>
-      <c r="K354" s="18"/>
+      <c r="K354" s="17"/>
       <c r="L354" s="6" t="s">
         <v>509</v>
       </c>
       <c r="M354" s="6"/>
     </row>
-    <row r="355" spans="1:13">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
         <v>352</v>
       </c>
@@ -16174,10 +16158,10 @@
       <c r="C355" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D355" s="13" t="s">
+      <c r="D355" s="16" t="s">
         <v>1002</v>
       </c>
-      <c r="E355" s="13"/>
+      <c r="E355" s="17"/>
       <c r="F355" s="6" t="s">
         <v>122</v>
       </c>
@@ -16190,16 +16174,16 @@
       <c r="I355" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="J355" s="17" t="s">
+      <c r="J355" s="20" t="s">
         <v>999</v>
       </c>
-      <c r="K355" s="18"/>
+      <c r="K355" s="17"/>
       <c r="L355" s="6" t="s">
         <v>509</v>
       </c>
       <c r="M355" s="6"/>
     </row>
-    <row r="356" spans="1:13">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
         <v>353</v>
       </c>
@@ -16209,10 +16193,10 @@
       <c r="C356" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D356" s="13" t="s">
+      <c r="D356" s="16" t="s">
         <v>1004</v>
       </c>
-      <c r="E356" s="13"/>
+      <c r="E356" s="17"/>
       <c r="F356" s="6" t="s">
         <v>122</v>
       </c>
@@ -16225,51 +16209,51 @@
       <c r="I356" s="6" t="s">
         <v>507</v>
       </c>
-      <c r="J356" s="17" t="s">
+      <c r="J356" s="20" t="s">
         <v>1005</v>
       </c>
-      <c r="K356" s="18"/>
+      <c r="K356" s="17"/>
       <c r="L356" s="6" t="s">
         <v>509</v>
       </c>
       <c r="M356" s="6"/>
     </row>
-    <row r="357" spans="1:13">
-      <c r="A357" s="20">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A357" s="13">
         <v>354</v>
       </c>
-      <c r="B357" s="19">
+      <c r="B357" s="12">
         <v>46218</v>
       </c>
-      <c r="C357" s="19" t="s">
+      <c r="C357" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D357" s="28" t="s">
+      <c r="D357" s="18" t="s">
         <v>1006</v>
       </c>
-      <c r="E357" s="28"/>
-      <c r="F357" s="20" t="s">
+      <c r="E357" s="19"/>
+      <c r="F357" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="G357" s="20" t="s">
+      <c r="G357" s="13" t="s">
         <v>959</v>
       </c>
-      <c r="H357" s="20" t="s">
+      <c r="H357" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="I357" s="20" t="s">
+      <c r="I357" s="13" t="s">
         <v>507</v>
       </c>
-      <c r="J357" s="27" t="s">
+      <c r="J357" s="21" t="s">
         <v>1007</v>
       </c>
-      <c r="K357" s="26"/>
-      <c r="L357" s="20" t="s">
+      <c r="K357" s="19"/>
+      <c r="L357" s="13" t="s">
         <v>509</v>
       </c>
-      <c r="M357" s="20"/>
-    </row>
-    <row r="358" spans="1:13" ht="30.75">
+      <c r="M357" s="13"/>
+    </row>
+    <row r="358" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
         <v>355</v>
       </c>
@@ -16279,10 +16263,10 @@
       <c r="C358" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D358" s="13" t="s">
+      <c r="D358" s="16" t="s">
         <v>1008</v>
       </c>
-      <c r="E358" s="13"/>
+      <c r="E358" s="17"/>
       <c r="F358" s="6" t="s">
         <v>780</v>
       </c>
@@ -16295,16 +16279,16 @@
       <c r="I358" s="6" t="s">
         <v>917</v>
       </c>
-      <c r="J358" s="12" t="s">
+      <c r="J358" s="20" t="s">
         <v>1009</v>
       </c>
-      <c r="K358" s="12"/>
+      <c r="K358" s="17"/>
       <c r="L358" s="6" t="s">
         <v>509</v>
       </c>
       <c r="M358" s="6"/>
     </row>
-    <row r="359" spans="1:13">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
         <v>356</v>
       </c>
@@ -16314,10 +16298,10 @@
       <c r="C359" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D359" s="17" t="s">
+      <c r="D359" s="20" t="s">
         <v>1010</v>
       </c>
-      <c r="E359" s="18"/>
+      <c r="E359" s="17"/>
       <c r="F359" s="6" t="s">
         <v>1011</v>
       </c>
@@ -16330,307 +16314,61 @@
       <c r="I359" s="6" t="s">
         <v>1014</v>
       </c>
-      <c r="J359" s="17" t="s">
+      <c r="J359" s="20" t="s">
         <v>1015</v>
       </c>
-      <c r="K359" s="18"/>
+      <c r="K359" s="17"/>
       <c r="L359" s="6" t="s">
         <v>509</v>
       </c>
       <c r="M359" s="6"/>
     </row>
+    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B360"/>
+    </row>
+    <row r="361" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B361"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:N2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:N2"/>
   <mergeCells count="35">
-    <mergeCell ref="D359:E359"/>
-    <mergeCell ref="J359:K359"/>
-    <mergeCell ref="D356:E356"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="J355:K355"/>
+    <mergeCell ref="D357:E357"/>
+    <mergeCell ref="J351:K351"/>
+    <mergeCell ref="J357:K357"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="L2:L3"/>
     <mergeCell ref="J356:K356"/>
-    <mergeCell ref="D357:E357"/>
-    <mergeCell ref="J357:K357"/>
-    <mergeCell ref="D358:E358"/>
-    <mergeCell ref="J358:K358"/>
     <mergeCell ref="D353:E353"/>
     <mergeCell ref="J353:K353"/>
+    <mergeCell ref="D349:E349"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="D359:E359"/>
+    <mergeCell ref="J348:K348"/>
+    <mergeCell ref="D350:E350"/>
+    <mergeCell ref="D355:E355"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D352:E352"/>
+    <mergeCell ref="J359:K359"/>
+    <mergeCell ref="D351:E351"/>
+    <mergeCell ref="D358:E358"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="H2:H3"/>
     <mergeCell ref="D354:E354"/>
+    <mergeCell ref="J349:K349"/>
+    <mergeCell ref="J350:K350"/>
+    <mergeCell ref="J358:K358"/>
+    <mergeCell ref="J352:K352"/>
+    <mergeCell ref="D356:E356"/>
     <mergeCell ref="J354:K354"/>
-    <mergeCell ref="D355:E355"/>
-    <mergeCell ref="J355:K355"/>
-    <mergeCell ref="D350:E350"/>
-    <mergeCell ref="J350:K350"/>
-    <mergeCell ref="D351:E351"/>
-    <mergeCell ref="J351:K351"/>
-    <mergeCell ref="D352:E352"/>
-    <mergeCell ref="J352:K352"/>
-    <mergeCell ref="J348:K348"/>
-    <mergeCell ref="D349:E349"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="M2:M3"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="J349:K349"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ffec3ae9-8fcb-4d01-9912-d9c8acfa0edd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="f744fce7-bf87-44de-8eb1-9fa1455f46be" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ffec3ae9-8fcb-4d01-9912-d9c8acfa0edd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010086942A3F34A68F4FA889A03CFBAE991E" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a9c9023ec2ee2a8c54e6ffbc5348479d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ffec3ae9-8fcb-4d01-9912-d9c8acfa0edd" xmlns:ns3="f744fce7-bf87-44de-8eb1-9fa1455f46be" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="976732c5a9512de0261515c98037693f" ns2:_="" ns3:_="">
-    <xsd:import namespace="ffec3ae9-8fcb-4d01-9912-d9c8acfa0edd"/>
-    <xsd:import namespace="f744fce7-bf87-44de-8eb1-9fa1455f46be"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ffec3ae9-8fcb-4d01-9912-d9c8acfa0edd" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_Flow_SignoffStatus" ma:index="12" nillable="true" ma:displayName="Estado de aprobación" ma:internalName="Estado_x0020_de_x0020_aprobaci_x00f3_n">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="5a12d170-c9fa-4ea1-b562-50058c25ba46" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="22" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f744fce7-bf87-44de-8eb1-9fa1455f46be" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="15" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{3c1456d8-15fc-47f4-a913-1f09bcca3391}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="f744fce7-bf87-44de-8eb1-9fa1455f46be">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7F4C917-C929-4E8D-89EB-6D6A5A32B05F}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{198F9FE4-CC7D-449E-8B79-8976DE4CC7F7}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B182A765-8CFD-450C-AF9F-37AEC630B2B6}"/>
 </file>
--- a/data/condiciones.xlsx
+++ b/data/condiciones.xlsx
@@ -1,26 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://novacero-my.sharepoint.com/personal/guilcapip_novacero_com/Documents/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mayancelad\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BE9FFAE-C1C2-4940-8F57-0E188F533447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10152"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="Listas" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$N$477</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Listas!$B$1:$I$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$N$477</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3209" uniqueCount="1230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3220" uniqueCount="1230">
   <si>
     <t>BASE CONDICIONES Y ACCIONES  INSEGURAS 2026</t>
   </si>
@@ -3840,7 +3839,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3">
     <font>
       <sz val="11"/>
@@ -4281,11 +4280,23 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4306,18 +4317,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4599,26 +4598,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:DQ477"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="11.42578125" style="3"/>
-    <col min="3" max="3" width="34.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="3"/>
+    <col min="3" max="3" width="34.109375" customWidth="1"/>
     <col min="4" max="4" width="85" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="61.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="61.33203125" customWidth="1"/>
+    <col min="7" max="7" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.44140625" customWidth="1"/>
     <col min="9" max="9" width="38" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="21.85546875" customWidth="1"/>
-    <col min="14" max="14" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.109375" customWidth="1"/>
+    <col min="11" max="11" width="20.6640625" customWidth="1"/>
+    <col min="12" max="12" width="21.88671875" customWidth="1"/>
+    <col min="14" max="14" width="34.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="91.5">
+    <row r="1" spans="1:14" ht="86.4">
       <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
@@ -4631,72 +4629,72 @@
       <c r="H1" s="35"/>
       <c r="I1" s="35"/>
       <c r="J1" s="35"/>
-      <c r="K1" s="69" t="s">
+      <c r="K1" s="73" t="s">
         <v>1</v>
       </c>
       <c r="L1" s="35"/>
       <c r="M1" s="35"/>
       <c r="N1" s="36"/>
     </row>
-    <row r="2" spans="1:14" s="62" customFormat="1" ht="22.5" hidden="1" customHeight="1">
-      <c r="A2" s="66" t="s">
+    <row r="2" spans="1:14" s="62" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="66" t="s">
+      <c r="C2" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="66" t="s">
+      <c r="D2" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="66" t="s">
+      <c r="E2" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="66" t="s">
+      <c r="F2" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="66" t="s">
+      <c r="G2" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="66" t="s">
+      <c r="H2" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="66" t="s">
+      <c r="I2" s="70" t="s">
         <v>10</v>
       </c>
       <c r="J2" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="70"/>
-      <c r="L2" s="67" t="s">
+      <c r="K2" s="74"/>
+      <c r="L2" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="66" t="s">
+      <c r="M2" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="66" t="s">
+      <c r="N2" s="70" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="62" customFormat="1" ht="22.5" hidden="1" customHeight="1">
-      <c r="A3" s="66"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
+    <row r="3" spans="1:14" s="62" customFormat="1" ht="22.5" customHeight="1">
+      <c r="A3" s="70"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
+      <c r="I3" s="70"/>
       <c r="J3" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="71"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="66"/>
-      <c r="N3" s="66"/>
+      <c r="K3" s="75"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="70"/>
+      <c r="N3" s="70"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="1">
@@ -7736,7 +7734,7 @@
       </c>
       <c r="N77" s="1"/>
     </row>
-    <row r="78" spans="1:14" ht="76.5" hidden="1">
+    <row r="78" spans="1:14" ht="43.2">
       <c r="A78" s="37">
         <v>75</v>
       </c>
@@ -8015,7 +8013,7 @@
       </c>
       <c r="N84" s="1"/>
     </row>
-    <row r="85" spans="1:14" hidden="1">
+    <row r="85" spans="1:14">
       <c r="A85" s="37">
         <v>82</v>
       </c>
@@ -9092,7 +9090,7 @@
       </c>
       <c r="N111" s="1"/>
     </row>
-    <row r="112" spans="1:14" ht="91.5">
+    <row r="112" spans="1:14" ht="43.2">
       <c r="A112" s="37">
         <v>109</v>
       </c>
@@ -10935,7 +10933,7 @@
       </c>
       <c r="N157" s="1"/>
     </row>
-    <row r="158" spans="1:14" ht="30.75">
+    <row r="158" spans="1:14" ht="28.8">
       <c r="A158" s="37">
         <v>155</v>
       </c>
@@ -13298,7 +13296,7 @@
       </c>
       <c r="N216" s="1"/>
     </row>
-    <row r="217" spans="1:14" hidden="1">
+    <row r="217" spans="1:14">
       <c r="A217" s="37">
         <v>214</v>
       </c>
@@ -14895,7 +14893,7 @@
       </c>
       <c r="N256" s="1"/>
     </row>
-    <row r="257" spans="1:14" ht="30.75">
+    <row r="257" spans="1:14" ht="28.8">
       <c r="A257" s="37">
         <v>254</v>
       </c>
@@ -18492,7 +18490,7 @@
       </c>
       <c r="N347" s="8"/>
     </row>
-    <row r="348" spans="1:14" ht="30.75">
+    <row r="348" spans="1:14" ht="28.8">
       <c r="A348" s="6">
         <v>345</v>
       </c>
@@ -18517,10 +18515,10 @@
       <c r="H348" s="11" t="s">
         <v>978</v>
       </c>
-      <c r="I348" s="63" t="s">
+      <c r="I348" s="68" t="s">
         <v>979</v>
       </c>
-      <c r="J348" s="63"/>
+      <c r="J348" s="68"/>
       <c r="K348" s="29"/>
       <c r="L348" s="2">
         <f t="shared" si="42"/>
@@ -18557,10 +18555,10 @@
       <c r="H349" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="I349" s="64" t="s">
+      <c r="I349" s="65" t="s">
         <v>983</v>
       </c>
-      <c r="J349" s="64"/>
+      <c r="J349" s="65"/>
       <c r="K349" s="38"/>
       <c r="L349" s="38"/>
       <c r="M349" s="40" t="str">
@@ -18594,10 +18592,10 @@
       <c r="H350" s="42" t="s">
         <v>896</v>
       </c>
-      <c r="I350" s="74" t="s">
+      <c r="I350" s="63" t="s">
         <v>986</v>
       </c>
-      <c r="J350" s="75"/>
+      <c r="J350" s="64"/>
       <c r="K350" s="38"/>
       <c r="L350" s="38"/>
       <c r="M350" s="40" t="str">
@@ -18631,10 +18629,10 @@
       <c r="H351" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="I351" s="74" t="s">
+      <c r="I351" s="63" t="s">
         <v>989</v>
       </c>
-      <c r="J351" s="75"/>
+      <c r="J351" s="64"/>
       <c r="K351" s="38"/>
       <c r="L351" s="38"/>
       <c r="M351" s="40" t="str">
@@ -18668,10 +18666,10 @@
       <c r="H352" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="I352" s="74" t="s">
+      <c r="I352" s="63" t="s">
         <v>989</v>
       </c>
-      <c r="J352" s="75"/>
+      <c r="J352" s="64"/>
       <c r="K352" s="38"/>
       <c r="L352" s="38"/>
       <c r="M352" s="40" t="str">
@@ -18705,10 +18703,10 @@
       <c r="H353" s="47" t="s">
         <v>912</v>
       </c>
-      <c r="I353" s="72" t="s">
+      <c r="I353" s="66" t="s">
         <v>993</v>
       </c>
-      <c r="J353" s="73"/>
+      <c r="J353" s="67"/>
       <c r="K353" s="38"/>
       <c r="L353" s="38"/>
       <c r="M353" s="40" t="str">
@@ -18742,10 +18740,10 @@
       <c r="H354" s="47" t="s">
         <v>912</v>
       </c>
-      <c r="I354" s="72" t="s">
+      <c r="I354" s="66" t="s">
         <v>995</v>
       </c>
-      <c r="J354" s="73"/>
+      <c r="J354" s="67"/>
       <c r="K354" s="38"/>
       <c r="L354" s="38"/>
       <c r="M354" s="40" t="str">
@@ -18779,10 +18777,10 @@
       <c r="H355" s="47" t="s">
         <v>502</v>
       </c>
-      <c r="I355" s="72" t="s">
+      <c r="I355" s="66" t="s">
         <v>993</v>
       </c>
-      <c r="J355" s="73"/>
+      <c r="J355" s="67"/>
       <c r="K355" s="38"/>
       <c r="L355" s="38"/>
       <c r="M355" s="40" t="str">
@@ -18816,10 +18814,10 @@
       <c r="H356" s="47" t="s">
         <v>502</v>
       </c>
-      <c r="I356" s="72" t="s">
+      <c r="I356" s="66" t="s">
         <v>999</v>
       </c>
-      <c r="J356" s="73"/>
+      <c r="J356" s="67"/>
       <c r="K356" s="38"/>
       <c r="L356" s="38"/>
       <c r="M356" s="40" t="str">
@@ -18853,10 +18851,10 @@
       <c r="H357" s="42" t="s">
         <v>502</v>
       </c>
-      <c r="I357" s="74" t="s">
+      <c r="I357" s="63" t="s">
         <v>1001</v>
       </c>
-      <c r="J357" s="75"/>
+      <c r="J357" s="64"/>
       <c r="K357" s="38"/>
       <c r="L357" s="38"/>
       <c r="M357" s="40" t="str">
@@ -18890,10 +18888,10 @@
       <c r="H358" s="47" t="s">
         <v>912</v>
       </c>
-      <c r="I358" s="64" t="s">
+      <c r="I358" s="65" t="s">
         <v>1003</v>
       </c>
-      <c r="J358" s="64"/>
+      <c r="J358" s="65"/>
       <c r="K358" s="38"/>
       <c r="L358" s="38"/>
       <c r="M358" s="40" t="str">
@@ -18927,10 +18925,10 @@
       <c r="H359" s="47" t="s">
         <v>1008</v>
       </c>
-      <c r="I359" s="64" t="s">
+      <c r="I359" s="65" t="s">
         <v>1009</v>
       </c>
-      <c r="J359" s="64"/>
+      <c r="J359" s="65"/>
       <c r="K359" s="38"/>
       <c r="L359" s="38"/>
       <c r="M359" s="40" t="str">
@@ -18964,10 +18962,10 @@
       <c r="H360" s="42" t="s">
         <v>793</v>
       </c>
-      <c r="I360" s="74" t="s">
+      <c r="I360" s="63" t="s">
         <v>1013</v>
       </c>
-      <c r="J360" s="75"/>
+      <c r="J360" s="64"/>
       <c r="K360" s="38"/>
       <c r="L360" s="38"/>
       <c r="M360" s="40" t="str">
@@ -19018,7 +19016,7 @@
     </row>
     <row r="362" spans="1:14" ht="27" customHeight="1">
       <c r="A362" s="47">
-        <f t="shared" ref="A362:A419" si="45">A361+1</f>
+        <f t="shared" ref="A362:A418" si="45">A361+1</f>
         <v>359</v>
       </c>
       <c r="B362" s="46">
@@ -19236,9 +19234,8 @@
       <c r="F367" s="47" t="s">
         <v>1025</v>
       </c>
-      <c r="G367" s="47" t="str">
-        <f>VLOOKUP(E367,Listas!$E$2:$H$45,2,0)</f>
-        <v>Mantenimiento Elétrico</v>
+      <c r="G367" s="42" t="s">
+        <v>1012</v>
       </c>
       <c r="H367" s="47" t="str">
         <f>VLOOKUP(E367,Listas!$E$2:$G$45,3,0)</f>
@@ -19558,9 +19555,8 @@
       <c r="F375" s="47" t="s">
         <v>1025</v>
       </c>
-      <c r="G375" s="47" t="str">
-        <f>VLOOKUP(E375,Listas!$E$2:$H$45,2,0)</f>
-        <v>Mantenimiento Elétrico</v>
+      <c r="G375" s="42" t="s">
+        <v>1012</v>
       </c>
       <c r="H375" s="47" t="str">
         <f>VLOOKUP(E375,Listas!$E$2:$G$45,3,0)</f>
@@ -19890,9 +19886,8 @@
       <c r="F383" s="47" t="s">
         <v>1025</v>
       </c>
-      <c r="G383" s="47" t="str">
-        <f>VLOOKUP(E383,Listas!$E$2:$H$45,2,0)</f>
-        <v>Mantenimiento Elétrico</v>
+      <c r="G383" s="42" t="s">
+        <v>1012</v>
       </c>
       <c r="H383" s="47" t="str">
         <f>VLOOKUP(E383,Listas!$E$2:$G$45,3,0)</f>
@@ -20132,9 +20127,8 @@
       <c r="F389" s="47" t="s">
         <v>1069</v>
       </c>
-      <c r="G389" s="47" t="str">
-        <f>VLOOKUP(E389,Listas!$E$2:$H$45,2,0)</f>
-        <v>Mantenimiento Elétrico</v>
+      <c r="G389" s="42" t="s">
+        <v>1012</v>
       </c>
       <c r="H389" s="47" t="str">
         <f>VLOOKUP(E389,Listas!$E$2:$G$45,3,0)</f>
@@ -20274,7 +20268,7 @@
       </c>
       <c r="N392" s="5"/>
     </row>
-    <row r="393" spans="1:14" ht="30.75">
+    <row r="393" spans="1:14" ht="28.8">
       <c r="A393" s="47">
         <f t="shared" si="45"/>
         <v>390</v>
@@ -20338,9 +20332,8 @@
       <c r="F394" s="47" t="s">
         <v>1052</v>
       </c>
-      <c r="G394" s="47" t="str">
-        <f>VLOOKUP(E394,Listas!$E$2:$H$45,2,0)</f>
-        <v>Mantenimiento Elétrico</v>
+      <c r="G394" s="42" t="s">
+        <v>1012</v>
       </c>
       <c r="H394" s="47" t="str">
         <f>VLOOKUP(E394,Listas!$E$2:$G$45,3,0)</f>
@@ -20632,9 +20625,8 @@
       <c r="F401" s="47" t="s">
         <v>1094</v>
       </c>
-      <c r="G401" s="47" t="str">
-        <f>VLOOKUP(E401,Listas!$E$2:$H$45,2,0)</f>
-        <v>Mantenimiento Elétrico</v>
+      <c r="G401" s="42" t="s">
+        <v>1012</v>
       </c>
       <c r="H401" s="47" t="str">
         <f>VLOOKUP(E401,Listas!$E$2:$G$45,3,0)</f>
@@ -20838,9 +20830,8 @@
       <c r="F406" s="5" t="s">
         <v>1077</v>
       </c>
-      <c r="G406" s="5" t="str">
-        <f>VLOOKUP(E406,Listas!$E$2:$H$45,2,0)</f>
-        <v>Mantenimiento Elétrico</v>
+      <c r="G406" s="42" t="s">
+        <v>1012</v>
       </c>
       <c r="H406" s="5" t="str">
         <f>VLOOKUP(E406,Listas!$E$2:$G$45,3,0)</f>
@@ -21887,9 +21878,8 @@
       <c r="F429" s="47" t="s">
         <v>1094</v>
       </c>
-      <c r="G429" s="47" t="str">
-        <f>VLOOKUP(E429,Listas!$E$2:$H$45,2,0)</f>
-        <v>Mantenimiento Elétrico</v>
+      <c r="G429" s="42" t="s">
+        <v>1012</v>
       </c>
       <c r="H429" s="47" t="str">
         <f>VLOOKUP(E429,Listas!$E$2:$G$45,3,0)</f>
@@ -21927,9 +21917,8 @@
       <c r="F430" s="47" t="s">
         <v>1146</v>
       </c>
-      <c r="G430" s="47" t="str">
-        <f>VLOOKUP(E430,Listas!$E$2:$H$45,2,0)</f>
-        <v>Mantenimiento Elétrico</v>
+      <c r="G430" s="42" t="s">
+        <v>1012</v>
       </c>
       <c r="H430" s="47" t="str">
         <f>VLOOKUP(E430,Listas!$E$2:$G$45,3,0)</f>
@@ -21967,9 +21956,8 @@
       <c r="F431" s="47" t="s">
         <v>1148</v>
       </c>
-      <c r="G431" s="47" t="str">
-        <f>VLOOKUP(E431,Listas!$E$2:$H$45,2,0)</f>
-        <v>Mantenimiento Elétrico</v>
+      <c r="G431" s="42" t="s">
+        <v>1012</v>
       </c>
       <c r="H431" s="47" t="str">
         <f>VLOOKUP(E431,Listas!$E$2:$G$45,3,0)</f>
@@ -22791,7 +22779,7 @@
       </c>
       <c r="N451" s="47"/>
     </row>
-    <row r="452" spans="1:14" hidden="1">
+    <row r="452" spans="1:14">
       <c r="A452" s="47">
         <f t="shared" si="71"/>
         <v>449</v>
@@ -22831,7 +22819,7 @@
       </c>
       <c r="N452" s="47"/>
     </row>
-    <row r="453" spans="1:14" ht="30.75" hidden="1">
+    <row r="453" spans="1:14" ht="28.8">
       <c r="A453" s="47">
         <f t="shared" si="71"/>
         <v>450</v>
@@ -22873,7 +22861,7 @@
       </c>
       <c r="N453" s="47"/>
     </row>
-    <row r="454" spans="1:14" ht="30.75" hidden="1">
+    <row r="454" spans="1:14" ht="28.8">
       <c r="A454" s="47">
         <f t="shared" si="71"/>
         <v>451</v>
@@ -22913,7 +22901,7 @@
       </c>
       <c r="N454" s="47"/>
     </row>
-    <row r="455" spans="1:14" ht="45.75" hidden="1">
+    <row r="455" spans="1:14" ht="43.2">
       <c r="A455" s="47">
         <f t="shared" si="71"/>
         <v>452</v>
@@ -22933,9 +22921,8 @@
       <c r="F455" s="47" t="s">
         <v>1034</v>
       </c>
-      <c r="G455" s="47" t="str">
-        <f>VLOOKUP(E455,Listas!$E$2:$H$45,2,0)</f>
-        <v>Mantenimiento Elétrico</v>
+      <c r="G455" s="42" t="s">
+        <v>1012</v>
       </c>
       <c r="H455" s="47" t="str">
         <f>VLOOKUP(E455,Listas!$E$2:$G$45,3,0)</f>
@@ -22953,7 +22940,7 @@
       </c>
       <c r="N455" s="47"/>
     </row>
-    <row r="456" spans="1:14" ht="30.75" hidden="1">
+    <row r="456" spans="1:14" ht="28.8">
       <c r="A456" s="47">
         <f t="shared" si="71"/>
         <v>453</v>
@@ -22993,7 +22980,7 @@
       </c>
       <c r="N456" s="47"/>
     </row>
-    <row r="457" spans="1:14" hidden="1">
+    <row r="457" spans="1:14">
       <c r="A457" s="47">
         <f t="shared" si="71"/>
         <v>454</v>
@@ -23021,7 +23008,7 @@
       </c>
       <c r="N457" s="47"/>
     </row>
-    <row r="458" spans="1:14" hidden="1">
+    <row r="458" spans="1:14">
       <c r="A458" s="47">
         <f t="shared" si="71"/>
         <v>455</v>
@@ -23049,7 +23036,7 @@
       </c>
       <c r="N458" s="47"/>
     </row>
-    <row r="459" spans="1:14" hidden="1">
+    <row r="459" spans="1:14">
       <c r="A459" s="47">
         <f t="shared" si="71"/>
         <v>456</v>
@@ -23077,7 +23064,7 @@
       </c>
       <c r="N459" s="47"/>
     </row>
-    <row r="460" spans="1:14" hidden="1">
+    <row r="460" spans="1:14">
       <c r="A460" s="47">
         <f t="shared" si="71"/>
         <v>457</v>
@@ -23105,7 +23092,7 @@
       </c>
       <c r="N460" s="47"/>
     </row>
-    <row r="461" spans="1:14" hidden="1">
+    <row r="461" spans="1:14">
       <c r="A461" s="47">
         <f t="shared" si="71"/>
         <v>458</v>
@@ -23133,7 +23120,7 @@
       </c>
       <c r="N461" s="47"/>
     </row>
-    <row r="462" spans="1:14" hidden="1">
+    <row r="462" spans="1:14">
       <c r="A462" s="47">
         <f t="shared" si="71"/>
         <v>459</v>
@@ -23161,7 +23148,7 @@
       </c>
       <c r="N462" s="47"/>
     </row>
-    <row r="463" spans="1:14" hidden="1">
+    <row r="463" spans="1:14">
       <c r="A463" s="47">
         <f t="shared" si="71"/>
         <v>460</v>
@@ -23189,7 +23176,7 @@
       </c>
       <c r="N463" s="47"/>
     </row>
-    <row r="464" spans="1:14" hidden="1">
+    <row r="464" spans="1:14">
       <c r="A464" s="47">
         <f t="shared" si="71"/>
         <v>461</v>
@@ -23217,7 +23204,7 @@
       </c>
       <c r="N464" s="47"/>
     </row>
-    <row r="465" spans="1:14" hidden="1">
+    <row r="465" spans="1:14">
       <c r="A465" s="47">
         <f t="shared" si="71"/>
         <v>462</v>
@@ -23245,7 +23232,7 @@
       </c>
       <c r="N465" s="47"/>
     </row>
-    <row r="466" spans="1:14" hidden="1">
+    <row r="466" spans="1:14">
       <c r="A466" s="47">
         <f t="shared" si="71"/>
         <v>463</v>
@@ -23273,7 +23260,7 @@
       </c>
       <c r="N466" s="47"/>
     </row>
-    <row r="467" spans="1:14" hidden="1">
+    <row r="467" spans="1:14">
       <c r="A467" s="47">
         <f t="shared" si="71"/>
         <v>464</v>
@@ -23301,7 +23288,7 @@
       </c>
       <c r="N467" s="47"/>
     </row>
-    <row r="468" spans="1:14" hidden="1">
+    <row r="468" spans="1:14">
       <c r="A468" s="47">
         <f t="shared" si="71"/>
         <v>465</v>
@@ -23329,7 +23316,7 @@
       </c>
       <c r="N468" s="47"/>
     </row>
-    <row r="469" spans="1:14" hidden="1">
+    <row r="469" spans="1:14">
       <c r="A469" s="47">
         <f t="shared" si="71"/>
         <v>466</v>
@@ -23357,7 +23344,7 @@
       </c>
       <c r="N469" s="47"/>
     </row>
-    <row r="470" spans="1:14" hidden="1">
+    <row r="470" spans="1:14">
       <c r="A470" s="47">
         <f t="shared" si="71"/>
         <v>467</v>
@@ -23385,7 +23372,7 @@
       </c>
       <c r="N470" s="47"/>
     </row>
-    <row r="471" spans="1:14" hidden="1">
+    <row r="471" spans="1:14">
       <c r="A471" s="47">
         <f t="shared" si="71"/>
         <v>468</v>
@@ -23413,7 +23400,7 @@
       </c>
       <c r="N471" s="47"/>
     </row>
-    <row r="472" spans="1:14" hidden="1">
+    <row r="472" spans="1:14">
       <c r="A472" s="47">
         <f t="shared" si="71"/>
         <v>469</v>
@@ -23441,7 +23428,7 @@
       </c>
       <c r="N472" s="47"/>
     </row>
-    <row r="473" spans="1:14" hidden="1">
+    <row r="473" spans="1:14">
       <c r="A473" s="47">
         <f t="shared" si="71"/>
         <v>470</v>
@@ -23469,7 +23456,7 @@
       </c>
       <c r="N473" s="47"/>
     </row>
-    <row r="474" spans="1:14" hidden="1">
+    <row r="474" spans="1:14">
       <c r="A474" s="47">
         <f t="shared" si="71"/>
         <v>471</v>
@@ -23497,7 +23484,7 @@
       </c>
       <c r="N474" s="47"/>
     </row>
-    <row r="475" spans="1:14" hidden="1">
+    <row r="475" spans="1:14">
       <c r="A475" s="47">
         <f t="shared" si="71"/>
         <v>472</v>
@@ -23525,7 +23512,7 @@
       </c>
       <c r="N475" s="47"/>
     </row>
-    <row r="476" spans="1:14" hidden="1">
+    <row r="476" spans="1:14">
       <c r="A476" s="47">
         <f t="shared" si="71"/>
         <v>473</v>
@@ -23553,7 +23540,7 @@
       </c>
       <c r="N476" s="47"/>
     </row>
-    <row r="477" spans="1:14" hidden="1">
+    <row r="477" spans="1:14">
       <c r="A477" s="47">
         <f t="shared" si="71"/>
         <v>474</v>
@@ -23582,25 +23569,11 @@
       <c r="N477" s="47"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N477" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="12">
-      <filters>
-        <filter val="CERRADO"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:N477"/>
   <mergeCells count="26">
-    <mergeCell ref="I360:J360"/>
-    <mergeCell ref="I359:J359"/>
-    <mergeCell ref="I356:J356"/>
-    <mergeCell ref="I357:J357"/>
-    <mergeCell ref="I358:J358"/>
-    <mergeCell ref="I355:J355"/>
-    <mergeCell ref="I350:J350"/>
-    <mergeCell ref="I351:J351"/>
-    <mergeCell ref="I352:J352"/>
-    <mergeCell ref="I353:J353"/>
-    <mergeCell ref="I354:J354"/>
+    <mergeCell ref="I349:J349"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="K1:K3"/>
     <mergeCell ref="I348:J348"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="A2:A3"/>
@@ -23613,49 +23586,57 @@
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="I349:J349"/>
-    <mergeCell ref="L2:L3"/>
-    <mergeCell ref="K1:K3"/>
+    <mergeCell ref="I355:J355"/>
+    <mergeCell ref="I350:J350"/>
+    <mergeCell ref="I351:J351"/>
+    <mergeCell ref="I352:J352"/>
+    <mergeCell ref="I353:J353"/>
+    <mergeCell ref="I354:J354"/>
+    <mergeCell ref="I360:J360"/>
+    <mergeCell ref="I359:J359"/>
+    <mergeCell ref="I356:J356"/>
+    <mergeCell ref="I357:J357"/>
+    <mergeCell ref="I358:J358"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M4:M477" xr:uid="{38702437-D7FA-4B57-A409-6B92B42A4263}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M4:M477"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A2AE06E7-AB43-4250-BA80-766D5379B3F5}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Listas!$B$2:$B$3</xm:f>
           </x14:formula1>
           <xm:sqref>C4:C6 C361:C477</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FB0558B7-BA8F-4504-91BE-8A6DA16F11DA}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Listas!$D$2:$D$9</xm:f>
           </x14:formula1>
           <xm:sqref>G4:G6</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D170A794-8E96-448E-BCEC-32B7972AF666}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Listas!$H$2:$H$9</xm:f>
           </x14:formula1>
           <xm:sqref>H4:H6</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{007CA5F7-A0FF-4B80-957A-FDF2920F5784}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Listas!$E$2:$E$42</xm:f>
           </x14:formula1>
           <xm:sqref>F362 E457:E477 E361:E406 E408:E448 E450:E455</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{172775DF-ADF4-4108-BAC8-470BA9D35F71}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Listas!$E$2:$E$50</xm:f>
           </x14:formula1>
           <xm:sqref>E456</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{35FE3BFD-1582-430E-AEA6-2C8F9B3627C1}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Listas!$E$2:$E$60</xm:f>
           </x14:formula1>
@@ -23668,16 +23649,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{336FB0AF-58F1-43A6-9784-3DA8E5196C76}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:L46"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="3" width="22.7109375" customWidth="1"/>
+    <col min="2" max="3" width="22.6640625" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
-    <col min="5" max="7" width="27.28515625" customWidth="1"/>
-    <col min="8" max="8" width="27.140625" customWidth="1"/>
-    <col min="9" max="9" width="28.85546875" customWidth="1"/>
-    <col min="12" max="12" width="15.42578125" customWidth="1"/>
+    <col min="5" max="7" width="27.33203125" customWidth="1"/>
+    <col min="8" max="8" width="27.109375" customWidth="1"/>
+    <col min="9" max="9" width="28.88671875" customWidth="1"/>
+    <col min="12" max="12" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12">
@@ -24297,7 +24278,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:I34" xr:uid="{336FB0AF-58F1-43A6-9784-3DA8E5196C76}"/>
+  <autoFilter ref="B1:I34"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -24315,15 +24296,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010086942A3F34A68F4FA889A03CFBAE991E" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a9c9023ec2ee2a8c54e6ffbc5348479d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ffec3ae9-8fcb-4d01-9912-d9c8acfa0edd" xmlns:ns3="f744fce7-bf87-44de-8eb1-9fa1455f46be" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="976732c5a9512de0261515c98037693f" ns2:_="" ns3:_="">
     <xsd:import namespace="ffec3ae9-8fcb-4d01-9912-d9c8acfa0edd"/>
@@ -24542,14 +24514,49 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{198F9FE4-CC7D-449E-8B79-8976DE4CC7F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{198F9FE4-CC7D-449E-8B79-8976DE4CC7F7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ffec3ae9-8fcb-4d01-9912-d9c8acfa0edd"/>
+    <ds:schemaRef ds:uri="f744fce7-bf87-44de-8eb1-9fa1455f46be"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7F4C917-C929-4E8D-89EB-6D6A5A32B05F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B182A765-8CFD-450C-AF9F-37AEC630B2B6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ffec3ae9-8fcb-4d01-9912-d9c8acfa0edd"/>
+    <ds:schemaRef ds:uri="f744fce7-bf87-44de-8eb1-9fa1455f46be"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B182A765-8CFD-450C-AF9F-37AEC630B2B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7F4C917-C929-4E8D-89EB-6D6A5A32B05F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>